--- a/Arquivos_Origem/Registros_2026.xlsx
+++ b/Arquivos_Origem/Registros_2026.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transações" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transações'!$A$1:$J$1614</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transações'!$A$1:$J$1618</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1614"/>
+  <dimension ref="A1:J1618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -583,15 +583,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apt. Aju. - Energia Elétrica</t>
+          <t>Serviço Apartamento 42 - São Paulo (P 2)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-214.23</v>
+        <v>-2801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -606,17 +606,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -717,15 +712,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Serviço Apartamento 42 - São Paulo (P 2)</t>
+          <t>Apt. Aju. - Energia Elétrica</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-2801</v>
+        <v>-214.23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -740,12 +735,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -36283,11 +36283,11 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Pagamento do Imposto de Renda - exercício 2026 - ECA</t>
+          <t>Pagamento do Imposto de Renda - exercício 2026 - RECEITA FEDERAL</t>
         </is>
       </c>
       <c r="C809" s="3" t="n">
-        <v>-3235.6</v>
+        <v>-17186.44</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Pagamento do Imposto de Renda - exercício 2026 - IDOSOS</t>
+          <t>Pagamento do Imposto de Renda - exercício 2026 - ECA</t>
         </is>
       </c>
       <c r="C810" s="3" t="n">
@@ -36369,11 +36369,11 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Pagamento do Imposto de Renda - exercício 2026 - RECEITA FEDERAL</t>
+          <t>Pagamento do Imposto de Renda - exercício 2026 - IDOSOS</t>
         </is>
       </c>
       <c r="C811" s="3" t="n">
-        <v>-17186.44</v>
+        <v>-3235.6</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -36938,20 +36938,20 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Água mineral</t>
+          <t>Juros de Investimento - BB RF Ref DI Cash Pvt</t>
         </is>
       </c>
       <c r="C824" s="3" t="n">
-        <v>-5</v>
+        <v>8704.33</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Juros de Investimento</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>Carteira</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
@@ -36961,17 +36961,22 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>Financeiras</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -36981,15 +36986,15 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Juros de Investimento - BB RF Ref DI Cash Pvt</t>
+          <t>Ajuda a Casa do Pobre</t>
         </is>
       </c>
       <c r="C825" s="3" t="n">
-        <v>8704.33</v>
+        <v>-30</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Juros de Investimento</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -37004,22 +37009,17 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H825" t="inlineStr">
-        <is>
-          <t>Financeiras</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -37029,20 +37029,20 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Ajuda a Casa do Pobre</t>
+          <t>Água mineral</t>
         </is>
       </c>
       <c r="C826" s="3" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Carteira</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -37052,12 +37052,12 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
@@ -54412,15 +54412,15 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Celulares - VIVO</t>
+          <t>Juros de Investimentos - CRI HYPERA</t>
         </is>
       </c>
       <c r="C1217" s="3" t="n">
-        <v>-359.89</v>
+        <v>19215.18</v>
       </c>
       <c r="D1217" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Juros de Investimento</t>
         </is>
       </c>
       <c r="E1217" t="inlineStr">
@@ -54435,17 +54435,22 @@
       </c>
       <c r="G1217" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>Financeiras</t>
         </is>
       </c>
       <c r="I1217" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1217" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -54498,20 +54503,20 @@
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>Visita Técnico para conserto COIFA</t>
+          <t>Celulares - VIVO</t>
         </is>
       </c>
       <c r="C1219" s="3" t="n">
-        <v>-80</v>
+        <v>-359.89</v>
       </c>
       <c r="D1219" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Celular</t>
         </is>
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1219" t="inlineStr">
@@ -54521,17 +54526,12 @@
       </c>
       <c r="G1219" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1219" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1219" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1219" t="inlineStr">
@@ -54546,20 +54546,20 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Juros de Investimentos - CRI HYPERA</t>
+          <t>Visita Técnico para conserto COIFA</t>
         </is>
       </c>
       <c r="C1220" s="3" t="n">
-        <v>19215.18</v>
+        <v>-80</v>
       </c>
       <c r="D1220" t="inlineStr">
         <is>
-          <t>Juros de Investimento</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1220" t="inlineStr">
@@ -54569,22 +54569,22 @@
       </c>
       <c r="G1220" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1220" t="inlineStr">
         <is>
-          <t>Financeiras</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1220" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1220" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -54680,15 +54680,15 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Lanche com Gracinha</t>
+          <t>Café da manhã com Gracinha</t>
         </is>
       </c>
       <c r="C1223" s="3" t="n">
-        <v>-26.5</v>
+        <v>-42.14</v>
       </c>
       <c r="D1223" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Padaria</t>
         </is>
       </c>
       <c r="E1223" t="inlineStr">
@@ -54723,15 +54723,15 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Café da manhã com Gracinha</t>
+          <t>Lanche com Gracinha</t>
         </is>
       </c>
       <c r="C1224" s="3" t="n">
-        <v>-42.14</v>
+        <v>-26.5</v>
       </c>
       <c r="D1224" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1224" t="inlineStr">
@@ -63345,7 +63345,7 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Presente 01 (-10,00 EURO)</t>
+          <t>Sorvetes (-8,00 EURO)</t>
         </is>
       </c>
       <c r="C1418" s="3" t="n">
@@ -63353,7 +63353,7 @@
       </c>
       <c r="D1418" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1418" t="inlineStr">
@@ -63368,12 +63368,12 @@
       </c>
       <c r="G1418" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1418" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1418" t="inlineStr">
@@ -63431,7 +63431,7 @@
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Presente 02 (-6,00 EURO)</t>
+          <t>Presente 01 (-10,00 EURO)</t>
         </is>
       </c>
       <c r="C1420" s="3" t="n">
@@ -63474,7 +63474,7 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>Sorvetes (-8,00 EURO)</t>
+          <t>Presente 02 (-6,00 EURO)</t>
         </is>
       </c>
       <c r="C1421" s="3" t="n">
@@ -63482,7 +63482,7 @@
       </c>
       <c r="D1421" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1421" t="inlineStr">
@@ -63497,12 +63497,12 @@
       </c>
       <c r="G1421" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1421" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1421" t="inlineStr">
@@ -63603,7 +63603,7 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Lanche com Gracinha (-11,20 EURO)</t>
+          <t>Almoço com Gracinha (-23,00 EURO)</t>
         </is>
       </c>
       <c r="C1424" s="3" t="n">
@@ -63611,7 +63611,7 @@
       </c>
       <c r="D1424" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1424" t="inlineStr">
@@ -63775,7 +63775,7 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Almoço com Gracinha (-23,00 EURO)</t>
+          <t>Lanche com Gracinha (-11,20 EURO)</t>
         </is>
       </c>
       <c r="C1428" s="3" t="n">
@@ -63783,7 +63783,7 @@
       </c>
       <c r="D1428" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1428" t="inlineStr">
@@ -63861,15 +63861,15 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Lanche com Gracinha</t>
         </is>
       </c>
       <c r="C1430" s="3" t="n">
-        <v>-138.98</v>
+        <v>-42.7</v>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1430" t="inlineStr">
@@ -63884,12 +63884,12 @@
       </c>
       <c r="G1430" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1430" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1430" t="inlineStr">
@@ -63904,35 +63904,40 @@
       </c>
       <c r="B1431" t="inlineStr">
         <is>
-          <t>Lanche com Gracinha</t>
+          <t>Apt. Aju. - Condomínio</t>
         </is>
       </c>
       <c r="C1431" s="3" t="n">
-        <v>-42.7</v>
+        <v>-822.89</v>
       </c>
       <c r="D1431" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1431" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1431" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1431" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1431" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1431" t="inlineStr">
@@ -63947,15 +63952,15 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Apt. Aju. - Condomínio</t>
+          <t>Casa Aracaju - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1432" s="3" t="n">
-        <v>-822.89</v>
+        <v>-213.57</v>
       </c>
       <c r="D1432" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1432" t="inlineStr">
@@ -63995,20 +64000,20 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Energia Elétrica</t>
+          <t>Rendimentos Saldo Conta WISE</t>
         </is>
       </c>
       <c r="C1433" s="3" t="n">
-        <v>-213.57</v>
+        <v>37.28</v>
       </c>
       <c r="D1433" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Juros de Investimento</t>
         </is>
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão WISE</t>
         </is>
       </c>
       <c r="F1433" t="inlineStr">
@@ -64018,22 +64023,22 @@
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>RECEITAS</t>
         </is>
       </c>
       <c r="H1433" t="inlineStr">
         <is>
-          <t>Contas da casa</t>
+          <t>Financeiras</t>
         </is>
       </c>
       <c r="I1433" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1433" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -64043,45 +64048,40 @@
       </c>
       <c r="B1434" t="inlineStr">
         <is>
-          <t>Rendimentos Saldo Conta WISE</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1434" s="3" t="n">
-        <v>37.28</v>
+        <v>-138.98</v>
       </c>
       <c r="D1434" t="inlineStr">
         <is>
-          <t>Juros de Investimento</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1434" t="inlineStr">
         <is>
-          <t>Cartão WISE</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1434" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1434" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H1434" t="inlineStr">
-        <is>
-          <t>Financeiras</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1434" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1434" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -67785,35 +67785,35 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Água de côco</t>
         </is>
       </c>
       <c r="C1518" s="3" t="n">
-        <v>-95.97</v>
+        <v>-10</v>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1518" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1518" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1518" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1518" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1518" t="inlineStr">
@@ -67914,35 +67914,35 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Ajuda a Casa do Pobre</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1521" s="3" t="n">
-        <v>-30</v>
+        <v>-95.97</v>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1521" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1521" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1521" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1521" t="inlineStr">
@@ -67957,15 +67957,15 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Água de côco</t>
+          <t>Ajuda a Casa do Pobre</t>
         </is>
       </c>
       <c r="C1522" s="3" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E1522" t="inlineStr">
@@ -67980,12 +67980,12 @@
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I1522" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J1522" t="inlineStr">
@@ -68000,35 +68000,35 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Celulares - VIVO</t>
         </is>
       </c>
       <c r="C1523" s="3" t="n">
-        <v>-8.99</v>
+        <v>-359.89</v>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Celular</t>
         </is>
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1523" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1523" t="inlineStr">
@@ -68043,15 +68043,15 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Celulares - VIVO</t>
+          <t>Protetor Auricular (com abafador de ruído</t>
         </is>
       </c>
       <c r="C1524" s="3" t="n">
-        <v>-359.89</v>
+        <v>-51.99</v>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1524" t="inlineStr">
@@ -68066,12 +68066,12 @@
       </c>
       <c r="G1524" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1524" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1524" t="inlineStr">
@@ -68086,35 +68086,35 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Protetor Auricular (com abafador de ruído</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1525" s="3" t="n">
-        <v>-51.99</v>
+        <v>-19.99</v>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1525" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1525" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1525" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1525" t="inlineStr">
@@ -68129,15 +68129,15 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Produtos Químicos para limpeza de piso externo</t>
         </is>
       </c>
       <c r="C1526" s="3" t="n">
-        <v>-19.99</v>
+        <v>-73.5</v>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1526" t="inlineStr">
@@ -68152,12 +68152,12 @@
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1526" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1526" t="inlineStr">
@@ -68172,15 +68172,15 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Produtos Químicos para limpeza de piso externo</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1527" s="3" t="n">
-        <v>-73.5</v>
+        <v>-8.99</v>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1527" t="inlineStr">
@@ -68195,12 +68195,12 @@
       </c>
       <c r="G1527" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1527" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1527" t="inlineStr">
@@ -68258,20 +68258,20 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Pagamento DAE (09.2026) - Ivonilde</t>
+          <t>Sacos para os alimentos dos necessitados (1 / 2)</t>
         </is>
       </c>
       <c r="C1529" s="3" t="n">
-        <v>-445.76</v>
+        <v>-72</v>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>Encargos Empregados</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1529" t="inlineStr">
@@ -68281,12 +68281,12 @@
       </c>
       <c r="G1529" t="inlineStr">
         <is>
-          <t>EMPREGADOS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1529" t="inlineStr">
         <is>
-          <t>Despesas com empregados</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1529" t="inlineStr">
@@ -68301,20 +68301,20 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Frutas e verduras</t>
+          <t>Resgate de Investimento - BB RF DEB INC PVT</t>
         </is>
       </c>
       <c r="C1530" s="3" t="n">
-        <v>-238.59</v>
+        <v>100000</v>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1530" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1530" t="inlineStr">
@@ -68324,17 +68324,17 @@
       </c>
       <c r="G1530" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1530" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1530" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -68344,20 +68344,20 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Resgate de Investimento - BB RF DEB INC PVT</t>
+          <t>Frutas e verduras</t>
         </is>
       </c>
       <c r="C1531" s="3" t="n">
-        <v>100000</v>
+        <v>-238.59</v>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1531" t="inlineStr">
@@ -68367,17 +68367,17 @@
       </c>
       <c r="G1531" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1531" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1531" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68387,20 +68387,20 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Sacos para os alimentos dos necessitados (1 / 2)</t>
+          <t>Pagamento DAE (09.2026) - Ivonilde</t>
         </is>
       </c>
       <c r="C1532" s="3" t="n">
-        <v>-72</v>
+        <v>-445.76</v>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Encargos Empregados</t>
         </is>
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1532" t="inlineStr">
@@ -68410,12 +68410,12 @@
       </c>
       <c r="G1532" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>EMPREGADOS</t>
         </is>
       </c>
       <c r="I1532" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com empregados</t>
         </is>
       </c>
       <c r="J1532" t="inlineStr">
@@ -68430,40 +68430,40 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Aluguel de terno para Nicholas (1 / 2)</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1533" s="3" t="n">
-        <v>-175</v>
+        <v>-100000</v>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1533" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1533" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1533" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1533" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -68521,15 +68521,15 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Equipamento para interligar no ARZOPA</t>
         </is>
       </c>
       <c r="C1535" s="3" t="n">
-        <v>-100000</v>
+        <v>-159.47</v>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1535" t="inlineStr">
@@ -68544,17 +68544,17 @@
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1535" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1535" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
@@ -68564,106 +68564,111 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Café da manhã com Gracinha</t>
+          <t>Devolução do valor do equipamento da ARZOPA</t>
         </is>
       </c>
       <c r="C1536" s="3" t="n">
-        <v>-39.75</v>
+        <v>159.47</v>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Reembolso</t>
         </is>
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1536" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1536" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>Outras</t>
         </is>
       </c>
       <c r="I1536" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1536" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" s="2" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Devolução do valor da compra dia 08/10/2026</t>
         </is>
       </c>
       <c r="C1537" s="3" t="n">
-        <v>-53.66</v>
+        <v>228.92</v>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Reembolso</t>
         </is>
       </c>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1537" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1537" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>RECEITAS</t>
         </is>
       </c>
       <c r="H1537" t="inlineStr">
         <is>
-          <t>Manutenção e encargos</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="I1537" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1537" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" s="2" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Aluguel de terno para Nicholas (1 / 2)</t>
         </is>
       </c>
       <c r="C1538" s="3" t="n">
-        <v>-112.07</v>
+        <v>-175</v>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1538" t="inlineStr">
@@ -68678,17 +68683,12 @@
       </c>
       <c r="G1538" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1538" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1538" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1538" t="inlineStr">
@@ -68699,24 +68699,24 @@
     </row>
     <row r="1539">
       <c r="A1539" s="2" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Benefício PETROS II</t>
+          <t>Café da manhã com Gracinha</t>
         </is>
       </c>
       <c r="C1539" s="3" t="n">
-        <v>4694.46</v>
+        <v>-39.75</v>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>Benefícios Aposentadoria</t>
+          <t>Padaria</t>
         </is>
       </c>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1539" t="inlineStr">
@@ -68726,40 +68726,35 @@
       </c>
       <c r="G1539" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H1539" t="inlineStr">
-        <is>
-          <t>Trabalho e Benefícios</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1539" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1539" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" s="2" t="n">
-        <v>46318</v>
+        <v>46316</v>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Benefício PETROS</t>
+          <t>Remédios para Isadora</t>
         </is>
       </c>
       <c r="C1540" s="3" t="n">
-        <v>10524.94</v>
+        <v>-113.87</v>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>Benefícios Aposentadoria</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1540" t="inlineStr">
@@ -68774,88 +68769,83 @@
       </c>
       <c r="G1540" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H1540" t="inlineStr">
-        <is>
-          <t>Trabalho e Benefícios</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1540" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1540" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" s="2" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Benefício INSS</t>
+          <t>Lata de lixo e outros utensílios domésticos</t>
         </is>
       </c>
       <c r="C1541" s="3" t="n">
-        <v>6334.53</v>
+        <v>-53.66</v>
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>Benefícios Aposentadoria</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1541" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1541" t="inlineStr">
         <is>
-          <t>Trabalho e Benefícios</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1541" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1541" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" s="2" t="n">
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Casa Aracaju - Materiais para o jardim</t>
         </is>
       </c>
       <c r="C1542" s="3" t="n">
-        <v>-500</v>
+        <v>-112.07</v>
       </c>
       <c r="D1542" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1542" t="inlineStr">
@@ -68870,17 +68860,17 @@
       </c>
       <c r="G1542" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1542" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1542" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1542" t="inlineStr">
@@ -68891,19 +68881,19 @@
     </row>
     <row r="1543">
       <c r="A1543" s="2" t="n">
-        <v>46320</v>
+        <v>46318</v>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Link de Internet - CLARO</t>
+          <t>Benefício PETROS</t>
         </is>
       </c>
       <c r="C1543" s="3" t="n">
-        <v>-267.06</v>
+        <v>10524.94</v>
       </c>
       <c r="D1543" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Benefícios Aposentadoria</t>
         </is>
       </c>
       <c r="E1543" t="inlineStr">
@@ -68918,35 +68908,40 @@
       </c>
       <c r="G1543" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1543" t="inlineStr">
+        <is>
+          <t>Trabalho e Benefícios</t>
         </is>
       </c>
       <c r="I1543" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1543" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" s="2" t="n">
-        <v>46320</v>
+        <v>46318</v>
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Pagamento "DUO GOURMET"</t>
+          <t>Benefício PETROS II</t>
         </is>
       </c>
       <c r="C1544" s="3" t="n">
-        <v>-45</v>
+        <v>4694.46</v>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Benefícios Aposentadoria</t>
         </is>
       </c>
       <c r="E1544" t="inlineStr">
@@ -68961,35 +68956,40 @@
       </c>
       <c r="G1544" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1544" t="inlineStr">
+        <is>
+          <t>Trabalho e Benefícios</t>
         </is>
       </c>
       <c r="I1544" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1544" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" s="2" t="n">
-        <v>46320</v>
+        <v>46318</v>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Passagem GRU / AJU - ACMD e MGAP - 21/11/2026 (2 / 2)</t>
+          <t>Benefício INSS</t>
         </is>
       </c>
       <c r="C1545" s="3" t="n">
-        <v>-312</v>
+        <v>6334.53</v>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Benefícios Aposentadoria</t>
         </is>
       </c>
       <c r="E1545" t="inlineStr">
@@ -69004,40 +69004,40 @@
       </c>
       <c r="G1545" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>RECEITAS</t>
         </is>
       </c>
       <c r="H1545" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Trabalho e Benefícios</t>
         </is>
       </c>
       <c r="I1545" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1545" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" s="2" t="n">
-        <v>46322</v>
+        <v>46319</v>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
         </is>
       </c>
       <c r="C1546" s="3" t="n">
-        <v>-102.5</v>
+        <v>-500</v>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1546" t="inlineStr">
@@ -69052,12 +69052,17 @@
       </c>
       <c r="G1546" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1546" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1546" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1546" t="inlineStr">
@@ -69068,24 +69073,24 @@
     </row>
     <row r="1547">
       <c r="A1547" s="2" t="n">
-        <v>46322</v>
+        <v>46320</v>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Link de Internet - CLARO</t>
         </is>
       </c>
       <c r="C1547" s="3" t="n">
-        <v>-139</v>
+        <v>-267.06</v>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1547" t="inlineStr">
@@ -69095,40 +69100,40 @@
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1547" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1547" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" s="2" t="n">
-        <v>46323</v>
+        <v>46320</v>
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>TV SAMSUNG quarto do casal (6 / 8)</t>
+          <t>Passagem GRU / AJU - ACMD e MGAP - 21/11/2026 (2 / 2)</t>
         </is>
       </c>
       <c r="C1548" s="3" t="n">
-        <v>-337.49</v>
+        <v>-312</v>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1548" t="inlineStr">
@@ -69138,12 +69143,17 @@
       </c>
       <c r="G1548" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1548" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1548" t="inlineStr">
@@ -69154,19 +69164,19 @@
     </row>
     <row r="1549">
       <c r="A1549" s="2" t="n">
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Água e Esgoto</t>
+          <t>Pagamento "DUO GOURMET"</t>
         </is>
       </c>
       <c r="C1549" s="3" t="n">
-        <v>-108.5</v>
+        <v>-45</v>
       </c>
       <c r="D1549" t="inlineStr">
         <is>
-          <t>Água e Esgoto</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1549" t="inlineStr">
@@ -69181,17 +69191,12 @@
       </c>
       <c r="G1549" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1549" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1549" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1549" t="inlineStr">
@@ -69202,24 +69207,24 @@
     </row>
     <row r="1550">
       <c r="A1550" s="2" t="n">
-        <v>46327</v>
+        <v>46322</v>
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Cemitério Colina da Saudade 2026</t>
+          <t>Troca da bateria do MACBOOK PRO</t>
         </is>
       </c>
       <c r="C1550" s="3" t="n">
-        <v>-600</v>
+        <v>-102.5</v>
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1550" t="inlineStr">
@@ -69229,12 +69234,12 @@
       </c>
       <c r="G1550" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I1550" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J1550" t="inlineStr">
@@ -69245,24 +69250,24 @@
     </row>
     <row r="1551">
       <c r="A1551" s="2" t="n">
-        <v>46327</v>
+        <v>46322</v>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Seguro Apt Aracaju - Parcelas 3</t>
+          <t>Aquisição do celular MOTOROLA G86</t>
         </is>
       </c>
       <c r="C1551" s="3" t="n">
-        <v>-52.85</v>
+        <v>-139</v>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1551" t="inlineStr">
@@ -69272,40 +69277,40 @@
       </c>
       <c r="G1551" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1551" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1551" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" s="2" t="n">
-        <v>46328</v>
+        <v>46323</v>
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Seguro de Itens Pessoais</t>
+          <t>TV SAMSUNG quarto do casal (6 / 8)</t>
         </is>
       </c>
       <c r="C1552" s="3" t="n">
-        <v>-9.9</v>
+        <v>-337.49</v>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1552" t="inlineStr">
@@ -69315,12 +69320,12 @@
       </c>
       <c r="G1552" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1552" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1552" t="inlineStr">
@@ -69331,19 +69336,19 @@
     </row>
     <row r="1553">
       <c r="A1553" s="2" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>Apt. Aju. - Energia Elétrica</t>
+          <t>Casa Aracaju - Água e Esgoto</t>
         </is>
       </c>
       <c r="C1553" s="3" t="n">
-        <v>-169.78</v>
+        <v>-108.5</v>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Água e Esgoto</t>
         </is>
       </c>
       <c r="E1553" t="inlineStr">
@@ -69379,19 +69384,19 @@
     </row>
     <row r="1554">
       <c r="A1554" s="2" t="n">
-        <v>46329</v>
+        <v>46327</v>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
+          <t>Cemitério Colina da Saudade 2026</t>
         </is>
       </c>
       <c r="C1554" s="3" t="n">
-        <v>200000</v>
+        <v>-600</v>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1554" t="inlineStr">
@@ -69406,40 +69411,40 @@
       </c>
       <c r="G1554" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1554" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1554" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" s="2" t="n">
-        <v>46332</v>
+        <v>46327</v>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Filtro para a COIFA - CONSUL</t>
+          <t>Seguro Apt Aracaju - Parcelas 3</t>
         </is>
       </c>
       <c r="C1555" s="3" t="n">
-        <v>-138.27</v>
+        <v>-52.85</v>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>Cartão BB ELO</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1555" t="inlineStr">
@@ -69449,17 +69454,12 @@
       </c>
       <c r="G1555" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1555" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1555" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1555" t="inlineStr">
@@ -69470,19 +69470,19 @@
     </row>
     <row r="1556">
       <c r="A1556" s="2" t="n">
-        <v>46332</v>
+        <v>46328</v>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
+          <t>Seguro de Itens Pessoais</t>
         </is>
       </c>
       <c r="C1556" s="3" t="n">
-        <v>-17600</v>
+        <v>-9.9</v>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Equipamentos Eletrônicos</t>
         </is>
       </c>
       <c r="E1556" t="inlineStr">
@@ -69497,40 +69497,40 @@
       </c>
       <c r="G1556" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1556" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1556" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" s="2" t="n">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Película para RANGER XLT</t>
+          <t>Apt. Aju. - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1557" s="3" t="n">
-        <v>-100</v>
+        <v>-169.78</v>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -69540,17 +69540,17 @@
       </c>
       <c r="G1557" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1557" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1557" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1557" t="inlineStr">
@@ -69561,19 +69561,19 @@
     </row>
     <row r="1558">
       <c r="A1558" s="2" t="n">
-        <v>46333</v>
+        <v>46329</v>
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (01)</t>
+          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
         </is>
       </c>
       <c r="C1558" s="3" t="n">
-        <v>-1429.33</v>
+        <v>200000</v>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1558" t="inlineStr">
@@ -69588,40 +69588,35 @@
       </c>
       <c r="G1558" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1558" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1558" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1558" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" s="2" t="n">
-        <v>46334</v>
+        <v>46332</v>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
+          <t>Película para RANGER XLT</t>
         </is>
       </c>
       <c r="C1559" s="3" t="n">
-        <v>-540.29</v>
+        <v>-100</v>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1559" t="inlineStr">
@@ -69636,17 +69631,17 @@
       </c>
       <c r="G1559" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="H1559" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1559" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1559" t="inlineStr">
@@ -69657,24 +69652,24 @@
     </row>
     <row r="1560">
       <c r="A1560" s="2" t="n">
-        <v>46334</v>
+        <v>46332</v>
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
+          <t>Filtro para a COIFA - CONSUL</t>
         </is>
       </c>
       <c r="C1560" s="3" t="n">
-        <v>-124.64</v>
+        <v>-138.27</v>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Cartão BB ELO</t>
         </is>
       </c>
       <c r="F1560" t="inlineStr">
@@ -69684,17 +69679,17 @@
       </c>
       <c r="G1560" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1560" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1560" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1560" t="inlineStr">
@@ -69705,24 +69700,24 @@
     </row>
     <row r="1561">
       <c r="A1561" s="2" t="n">
-        <v>46334</v>
+        <v>46332</v>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Sapato para ACMD</t>
+          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
         </is>
       </c>
       <c r="C1561" s="3" t="n">
-        <v>-121.6</v>
+        <v>-17600</v>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1561" t="inlineStr">
@@ -69732,35 +69727,35 @@
       </c>
       <c r="G1561" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1561" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1561" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" s="2" t="n">
-        <v>46335</v>
+        <v>46333</v>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
+          <t>Apt. SP. - Condomínio (01)</t>
         </is>
       </c>
       <c r="C1562" s="3" t="n">
-        <v>300000</v>
+        <v>-1429.33</v>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1562" t="inlineStr">
@@ -69775,40 +69770,45 @@
       </c>
       <c r="G1562" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1562" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1562" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1562" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" s="2" t="n">
-        <v>46336</v>
+        <v>46334</v>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Mensalidade da hidroginástica (10 / 11)</t>
+          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
         </is>
       </c>
       <c r="C1563" s="3" t="n">
-        <v>-88</v>
+        <v>-124.64</v>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1563" t="inlineStr">
@@ -69818,12 +69818,17 @@
       </c>
       <c r="G1563" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1563" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1563" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1563" t="inlineStr">
@@ -69834,24 +69839,24 @@
     </row>
     <row r="1564">
       <c r="A1564" s="2" t="n">
-        <v>46336</v>
+        <v>46334</v>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Sapato para ACMD</t>
         </is>
       </c>
       <c r="C1564" s="3" t="n">
-        <v>-300000</v>
+        <v>-121.6</v>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1564" t="inlineStr">
@@ -69861,40 +69866,40 @@
       </c>
       <c r="G1564" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1564" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1564" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" s="2" t="n">
-        <v>46336</v>
+        <v>46334</v>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Hotel Stela Maris - Salvador</t>
+          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
         </is>
       </c>
       <c r="C1565" s="3" t="n">
-        <v>-69.37</v>
+        <v>-540.29</v>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1565" t="inlineStr">
@@ -69925,19 +69930,19 @@
     </row>
     <row r="1566">
       <c r="A1566" s="2" t="n">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Aplicação PGBL BRASILPREV - ACMD</t>
+          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
         </is>
       </c>
       <c r="C1566" s="3" t="n">
-        <v>-209.34</v>
+        <v>300000</v>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>BRASILPREV</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1566" t="inlineStr">
@@ -69957,12 +69962,12 @@
       </c>
       <c r="I1566" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1566" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -69972,15 +69977,15 @@
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Presentes comprados por Gracinha (2026.10.14)</t>
+          <t>Aplicação PGBL BRASILPREV - ACMD</t>
         </is>
       </c>
       <c r="C1567" s="3" t="n">
-        <v>-134.38</v>
+        <v>-209.34</v>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>BRASILPREV</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
@@ -69995,17 +70000,17 @@
       </c>
       <c r="G1567" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1567" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1567" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -70015,15 +70020,15 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>Plano OSAF - Serviços Funerários</t>
+          <t>Mensalidade da hidroginástica (10 / 11)</t>
         </is>
       </c>
       <c r="C1568" s="3" t="n">
-        <v>-82.64</v>
+        <v>-88</v>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1568" t="inlineStr">
@@ -70038,12 +70043,12 @@
       </c>
       <c r="G1568" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1568" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1568" t="inlineStr">
@@ -70054,24 +70059,24 @@
     </row>
     <row r="1569">
       <c r="A1569" s="2" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
+          <t>Plano OSAF - Serviços Funerários</t>
         </is>
       </c>
       <c r="C1569" s="3" t="n">
-        <v>-1818.04</v>
+        <v>-82.64</v>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1569" t="inlineStr">
@@ -70081,40 +70086,40 @@
       </c>
       <c r="G1569" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1569" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1569" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" s="2" t="n">
-        <v>46338</v>
+        <v>46336</v>
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>Aluguel do terno para o casamento de João Paulo</t>
+          <t>Hotel Stela Maris - Salvador</t>
         </is>
       </c>
       <c r="C1570" s="3" t="n">
-        <v>-116.67</v>
+        <v>-69.37</v>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1570" t="inlineStr">
@@ -70124,12 +70129,17 @@
       </c>
       <c r="G1570" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1570" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1570" t="inlineStr">
@@ -70140,24 +70150,24 @@
     </row>
     <row r="1571">
       <c r="A1571" s="2" t="n">
-        <v>46339</v>
+        <v>46336</v>
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
+          <t>Presentes comprados por Gracinha (2026.10.14)</t>
         </is>
       </c>
       <c r="C1571" s="3" t="n">
-        <v>-93.89</v>
+        <v>-134.38</v>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1571" t="inlineStr">
@@ -70167,17 +70177,12 @@
       </c>
       <c r="G1571" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1571" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1571" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1571" t="inlineStr">
@@ -70188,24 +70193,24 @@
     </row>
     <row r="1572">
       <c r="A1572" s="2" t="n">
-        <v>46339</v>
+        <v>46336</v>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>Seguro da Hilux SW4</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1572" s="3" t="n">
-        <v>-233.11</v>
+        <v>-300000</v>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1572" t="inlineStr">
@@ -70215,40 +70220,35 @@
       </c>
       <c r="G1572" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1572" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1572" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1572" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" s="2" t="n">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
+          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
         </is>
       </c>
       <c r="C1573" s="3" t="n">
-        <v>-58.07</v>
+        <v>-1818.04</v>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1573" t="inlineStr">
@@ -70268,30 +70268,30 @@
       </c>
       <c r="I1573" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1573" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" s="2" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Aluguel do terno para o casamento de João Paulo</t>
         </is>
       </c>
       <c r="C1574" s="3" t="n">
-        <v>-52.83</v>
+        <v>-116.67</v>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1574" t="inlineStr">
@@ -70306,12 +70306,12 @@
       </c>
       <c r="G1574" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1574" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1574" t="inlineStr">
@@ -70322,19 +70322,19 @@
     </row>
     <row r="1575">
       <c r="A1575" s="2" t="n">
-        <v>46341</v>
+        <v>46339</v>
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>Pagamento Clube SMILES</t>
+          <t>Seguro da Hilux SW4</t>
         </is>
       </c>
       <c r="C1575" s="3" t="n">
-        <v>-46</v>
+        <v>-233.11</v>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1575" t="inlineStr">
@@ -70349,17 +70349,17 @@
       </c>
       <c r="G1575" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="H1575" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1575" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1575" t="inlineStr">
@@ -70370,19 +70370,19 @@
     </row>
     <row r="1576">
       <c r="A1576" s="2" t="n">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Transporte Terrestre, Hoteis e Excursão</t>
+          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
         </is>
       </c>
       <c r="C1576" s="3" t="n">
-        <v>-1824.26</v>
+        <v>-58.07</v>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>VIAGENS/Passeios</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1576" t="inlineStr">
@@ -70397,40 +70397,35 @@
       </c>
       <c r="G1576" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1576" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1576" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1576" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" s="2" t="n">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Academia ACMD</t>
+          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
         </is>
       </c>
       <c r="C1577" s="3" t="n">
-        <v>-448.35</v>
+        <v>-93.89</v>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1577" t="inlineStr">
@@ -70445,12 +70440,17 @@
       </c>
       <c r="G1577" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1577" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1577" t="inlineStr">
@@ -70461,19 +70461,19 @@
     </row>
     <row r="1578">
       <c r="A1578" s="2" t="n">
-        <v>46345</v>
+        <v>46341</v>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1578" s="3" t="n">
-        <v>-8.99</v>
+        <v>-52.83</v>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1578" t="inlineStr">
@@ -70488,12 +70488,12 @@
       </c>
       <c r="G1578" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1578" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1578" t="inlineStr">
@@ -70504,19 +70504,19 @@
     </row>
     <row r="1579">
       <c r="A1579" s="2" t="n">
-        <v>46346</v>
+        <v>46341</v>
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Sacos para os alimentos dos necessitados (2 / 2)</t>
+          <t>Pagamento Clube SMILES</t>
         </is>
       </c>
       <c r="C1579" s="3" t="n">
-        <v>-72</v>
+        <v>-46</v>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1579" t="inlineStr">
@@ -70531,12 +70531,17 @@
       </c>
       <c r="G1579" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1579" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1579" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1579" t="inlineStr">
@@ -70547,19 +70552,19 @@
     </row>
     <row r="1580">
       <c r="A1580" s="2" t="n">
-        <v>46346</v>
+        <v>46342</v>
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>Materiais de limpeza (2 / 2)</t>
+          <t>Transporte Terrestre, Hoteis e Excursão</t>
         </is>
       </c>
       <c r="C1580" s="3" t="n">
-        <v>-110.2</v>
+        <v>-1824.26</v>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>VIAGENS/Passeios</t>
         </is>
       </c>
       <c r="E1580" t="inlineStr">
@@ -70574,12 +70579,17 @@
       </c>
       <c r="G1580" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1580" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1580" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1580" t="inlineStr">
@@ -70590,24 +70600,24 @@
     </row>
     <row r="1581">
       <c r="A1581" s="2" t="n">
-        <v>46347</v>
+        <v>46342</v>
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (02)</t>
+          <t>Academia ACMD</t>
         </is>
       </c>
       <c r="C1581" s="3" t="n">
-        <v>-1063.47</v>
+        <v>-448.35</v>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1581" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1581" t="inlineStr">
@@ -70617,17 +70627,12 @@
       </c>
       <c r="G1581" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1581" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1581" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1581" t="inlineStr">
@@ -70638,19 +70643,19 @@
     </row>
     <row r="1582">
       <c r="A1582" s="2" t="n">
-        <v>46347</v>
+        <v>46345</v>
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Aluguel de terno para Nicholas (2 / 2)</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1582" s="3" t="n">
-        <v>-175</v>
+        <v>-8.99</v>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1582" t="inlineStr">
@@ -70681,19 +70686,19 @@
     </row>
     <row r="1583">
       <c r="A1583" s="2" t="n">
-        <v>46348</v>
+        <v>46346</v>
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Materiais de limpeza (2 / 2)</t>
         </is>
       </c>
       <c r="C1583" s="3" t="n">
-        <v>-53.66</v>
+        <v>-110.2</v>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1583" t="inlineStr">
@@ -70708,17 +70713,12 @@
       </c>
       <c r="G1583" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1583" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1583" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1583" t="inlineStr">
@@ -70729,19 +70729,19 @@
     </row>
     <row r="1584">
       <c r="A1584" s="2" t="n">
-        <v>46348</v>
+        <v>46346</v>
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Sacos para os alimentos dos necessitados (2 / 2)</t>
         </is>
       </c>
       <c r="C1584" s="3" t="n">
-        <v>-112.07</v>
+        <v>-72</v>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1584" t="inlineStr">
@@ -70756,17 +70756,12 @@
       </c>
       <c r="G1584" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1584" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1584" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1584" t="inlineStr">
@@ -70777,19 +70772,19 @@
     </row>
     <row r="1585">
       <c r="A1585" s="2" t="n">
-        <v>46350</v>
+        <v>46347</v>
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Aluguel de terno para Nicholas (2 / 2)</t>
         </is>
       </c>
       <c r="C1585" s="3" t="n">
-        <v>-500</v>
+        <v>-175</v>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1585" t="inlineStr">
@@ -70804,17 +70799,12 @@
       </c>
       <c r="G1585" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1585" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1585" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1585" t="inlineStr">
@@ -70825,19 +70815,19 @@
     </row>
     <row r="1586">
       <c r="A1586" s="2" t="n">
-        <v>46351</v>
+        <v>46347</v>
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Pagamento "DUO GOURMET"</t>
+          <t>Apt. SP. - Condomínio (02)</t>
         </is>
       </c>
       <c r="C1586" s="3" t="n">
-        <v>-45</v>
+        <v>-1063.47</v>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1586" t="inlineStr">
@@ -70852,12 +70842,17 @@
       </c>
       <c r="G1586" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1586" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1586" t="inlineStr">
@@ -70868,19 +70863,19 @@
     </row>
     <row r="1587">
       <c r="A1587" s="2" t="n">
-        <v>46353</v>
+        <v>46348</v>
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Casa Aracaju - Materiais para o jardim</t>
         </is>
       </c>
       <c r="C1587" s="3" t="n">
-        <v>-102.5</v>
+        <v>-112.07</v>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1587" t="inlineStr">
@@ -70895,12 +70890,17 @@
       </c>
       <c r="G1587" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1587" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1587" t="inlineStr">
@@ -70911,19 +70911,19 @@
     </row>
     <row r="1588">
       <c r="A1588" s="2" t="n">
-        <v>46353</v>
+        <v>46348</v>
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Lata de lixo e outros utensílios domésticos</t>
         </is>
       </c>
       <c r="C1588" s="3" t="n">
-        <v>-139</v>
+        <v>-53.66</v>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1588" t="inlineStr">
@@ -70938,35 +70938,40 @@
       </c>
       <c r="G1588" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1588" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1588" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1588" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" s="2" t="n">
-        <v>46354</v>
+        <v>46350</v>
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>TV SAMSUNG quarto do casal (7 / 8)</t>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
         </is>
       </c>
       <c r="C1589" s="3" t="n">
-        <v>-337.49</v>
+        <v>-500</v>
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1589" t="inlineStr">
@@ -70981,12 +70986,17 @@
       </c>
       <c r="G1589" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1589" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1589" t="inlineStr">
@@ -70997,19 +71007,19 @@
     </row>
     <row r="1590">
       <c r="A1590" s="2" t="n">
-        <v>46357</v>
+        <v>46351</v>
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Seguro Apt Aracaju - Parcelas 4</t>
+          <t>Pagamento "DUO GOURMET"</t>
         </is>
       </c>
       <c r="C1590" s="3" t="n">
-        <v>-52.85</v>
+        <v>-45</v>
       </c>
       <c r="D1590" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1590" t="inlineStr">
@@ -71024,12 +71034,12 @@
       </c>
       <c r="G1590" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1590" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1590" t="inlineStr">
@@ -71040,24 +71050,24 @@
     </row>
     <row r="1591">
       <c r="A1591" s="2" t="n">
-        <v>46358</v>
+        <v>46353</v>
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Seguro de Itens Pessoais</t>
+          <t>Troca da bateria do MACBOOK PRO</t>
         </is>
       </c>
       <c r="C1591" s="3" t="n">
-        <v>-9.9</v>
+        <v>-102.5</v>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E1591" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1591" t="inlineStr">
@@ -71067,12 +71077,12 @@
       </c>
       <c r="G1591" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I1591" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J1591" t="inlineStr">
@@ -71083,19 +71093,19 @@
     </row>
     <row r="1592">
       <c r="A1592" s="2" t="n">
-        <v>46362</v>
+        <v>46353</v>
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>Película para RANGER XLT</t>
+          <t>Aquisição do celular MOTOROLA G86</t>
         </is>
       </c>
       <c r="C1592" s="3" t="n">
-        <v>-100</v>
+        <v>-139</v>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1592" t="inlineStr">
@@ -71110,45 +71120,40 @@
       </c>
       <c r="G1592" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1592" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1592" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1592" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" s="2" t="n">
-        <v>46362</v>
+        <v>46354</v>
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
+          <t>TV SAMSUNG quarto do casal (7 / 8)</t>
         </is>
       </c>
       <c r="C1593" s="3" t="n">
-        <v>-17600</v>
+        <v>-337.49</v>
       </c>
       <c r="D1593" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1593" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1593" t="inlineStr">
@@ -71158,40 +71163,40 @@
       </c>
       <c r="G1593" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1593" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1593" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" s="2" t="n">
-        <v>46364</v>
+        <v>46357</v>
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
+          <t>Seguro Apt Aracaju - Parcelas 4</t>
         </is>
       </c>
       <c r="C1594" s="3" t="n">
-        <v>-540.29</v>
+        <v>-52.85</v>
       </c>
       <c r="D1594" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="E1594" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1594" t="inlineStr">
@@ -71201,17 +71206,12 @@
       </c>
       <c r="G1594" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1594" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1594" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1594" t="inlineStr">
@@ -71222,24 +71222,24 @@
     </row>
     <row r="1595">
       <c r="A1595" s="2" t="n">
-        <v>46364</v>
+        <v>46358</v>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
+          <t>Seguro de Itens Pessoais</t>
         </is>
       </c>
       <c r="C1595" s="3" t="n">
-        <v>-124.64</v>
+        <v>-9.9</v>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Equipamentos Eletrônicos</t>
         </is>
       </c>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1595" t="inlineStr">
@@ -71249,17 +71249,12 @@
       </c>
       <c r="G1595" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1595" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1595" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1595" t="inlineStr">
@@ -71270,19 +71265,19 @@
     </row>
     <row r="1596">
       <c r="A1596" s="2" t="n">
-        <v>46366</v>
+        <v>46362</v>
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>Hotel Stela Maris - Salvador</t>
+          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
         </is>
       </c>
       <c r="C1596" s="3" t="n">
-        <v>-69.37</v>
+        <v>-17600</v>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1596" t="inlineStr">
@@ -71297,45 +71292,40 @@
       </c>
       <c r="G1596" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1596" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1596" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1596" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" s="2" t="n">
-        <v>46366</v>
+        <v>46362</v>
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Presentes comprados por Gracinha (2026.10.14)</t>
+          <t>Película para RANGER XLT</t>
         </is>
       </c>
       <c r="C1597" s="3" t="n">
-        <v>-134.38</v>
+        <v>-100</v>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1597" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1597" t="inlineStr">
@@ -71345,12 +71335,17 @@
       </c>
       <c r="G1597" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1597" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1597" t="inlineStr">
@@ -71361,24 +71356,24 @@
     </row>
     <row r="1598">
       <c r="A1598" s="2" t="n">
-        <v>46366</v>
+        <v>46364</v>
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>Aplicação PGBL BRASILPREV - ACMD</t>
+          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
         </is>
       </c>
       <c r="C1598" s="3" t="n">
-        <v>-209.34</v>
+        <v>-540.29</v>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>BRASILPREV</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1598" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1598" t="inlineStr">
@@ -71388,40 +71383,45 @@
       </c>
       <c r="G1598" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1598" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1598" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" s="2" t="n">
-        <v>46366</v>
+        <v>46364</v>
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Mensalidade da hidroginástica (11 / 11)</t>
+          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
         </is>
       </c>
       <c r="C1599" s="3" t="n">
-        <v>-23.46</v>
+        <v>-124.64</v>
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1599" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1599" t="inlineStr">
@@ -71431,12 +71431,17 @@
       </c>
       <c r="G1599" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1599" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1599" t="inlineStr">
@@ -71490,24 +71495,24 @@
     </row>
     <row r="1601">
       <c r="A1601" s="2" t="n">
-        <v>46367</v>
+        <v>46366</v>
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
+          <t>Hotel Stela Maris - Salvador</t>
         </is>
       </c>
       <c r="C1601" s="3" t="n">
-        <v>-1818.04</v>
+        <v>-69.37</v>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1601" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1601" t="inlineStr">
@@ -71517,40 +71522,45 @@
       </c>
       <c r="G1601" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1601" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1601" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" s="2" t="n">
-        <v>46369</v>
+        <v>46366</v>
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
+          <t>Aplicação PGBL BRASILPREV - ACMD</t>
         </is>
       </c>
       <c r="C1602" s="3" t="n">
-        <v>-93.89</v>
+        <v>-209.34</v>
       </c>
       <c r="D1602" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>BRASILPREV</t>
         </is>
       </c>
       <c r="E1602" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1602" t="inlineStr">
@@ -71560,45 +71570,40 @@
       </c>
       <c r="G1602" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1602" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1602" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1602" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" s="2" t="n">
-        <v>46369</v>
+        <v>46366</v>
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
+          <t>Presentes comprados por Gracinha (2026.10.14)</t>
         </is>
       </c>
       <c r="C1603" s="3" t="n">
-        <v>-58.07</v>
+        <v>-134.38</v>
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1603" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1603" t="inlineStr">
@@ -71608,40 +71613,40 @@
       </c>
       <c r="G1603" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1603" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1603" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" s="2" t="n">
-        <v>46369</v>
+        <v>46366</v>
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>Seguro da Hilux SW4</t>
+          <t>Mensalidade da hidroginástica (11 / 11)</t>
         </is>
       </c>
       <c r="C1604" s="3" t="n">
-        <v>-233.11</v>
+        <v>-23.46</v>
       </c>
       <c r="D1604" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1604" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1604" t="inlineStr">
@@ -71651,17 +71656,12 @@
       </c>
       <c r="G1604" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1604" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1604" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1604" t="inlineStr">
@@ -71672,19 +71672,19 @@
     </row>
     <row r="1605">
       <c r="A1605" s="2" t="n">
-        <v>46371</v>
+        <v>46367</v>
       </c>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>Pagamento Clube SMILES</t>
+          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
         </is>
       </c>
       <c r="C1605" s="3" t="n">
-        <v>-46</v>
+        <v>-1818.04</v>
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1605" t="inlineStr">
@@ -71699,40 +71699,35 @@
       </c>
       <c r="G1605" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1605" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1605" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1605" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" s="2" t="n">
-        <v>46371</v>
+        <v>46369</v>
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
         </is>
       </c>
       <c r="C1606" s="3" t="n">
-        <v>-52.83</v>
+        <v>-93.89</v>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1606" t="inlineStr">
@@ -71747,12 +71742,17 @@
       </c>
       <c r="G1606" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1606" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1606" t="inlineStr">
@@ -71763,19 +71763,19 @@
     </row>
     <row r="1607">
       <c r="A1607" s="2" t="n">
-        <v>46372</v>
+        <v>46369</v>
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Transporte Terrestre, Hoteis e Excursão</t>
+          <t>Seguro da Hilux SW4</t>
         </is>
       </c>
       <c r="C1607" s="3" t="n">
-        <v>-1824.26</v>
+        <v>-233.11</v>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>VIAGENS/Passeios</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1607" t="inlineStr">
@@ -71790,17 +71790,17 @@
       </c>
       <c r="G1607" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="H1607" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1607" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1607" t="inlineStr">
@@ -71811,19 +71811,19 @@
     </row>
     <row r="1608">
       <c r="A1608" s="2" t="n">
-        <v>46375</v>
+        <v>46369</v>
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
         </is>
       </c>
       <c r="C1608" s="3" t="n">
-        <v>-8.99</v>
+        <v>-58.07</v>
       </c>
       <c r="D1608" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1608" t="inlineStr">
@@ -71838,35 +71838,35 @@
       </c>
       <c r="G1608" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1608" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1608" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" s="2" t="n">
-        <v>46378</v>
+        <v>46371</v>
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Pagamento Clube SMILES</t>
         </is>
       </c>
       <c r="C1609" s="3" t="n">
-        <v>-112.07</v>
+        <v>-46</v>
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1609" t="inlineStr">
@@ -71881,17 +71881,17 @@
       </c>
       <c r="G1609" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1609" t="inlineStr">
         <is>
-          <t>Manutenção e encargos</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1609" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1609" t="inlineStr">
@@ -71902,19 +71902,19 @@
     </row>
     <row r="1610">
       <c r="A1610" s="2" t="n">
-        <v>46378</v>
+        <v>46371</v>
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1610" s="3" t="n">
-        <v>-53.66</v>
+        <v>-52.83</v>
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1610" t="inlineStr">
@@ -71929,17 +71929,12 @@
       </c>
       <c r="G1610" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1610" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1610" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1610" t="inlineStr">
@@ -71950,19 +71945,19 @@
     </row>
     <row r="1611">
       <c r="A1611" s="2" t="n">
-        <v>46380</v>
+        <v>46372</v>
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Transporte Terrestre, Hoteis e Excursão</t>
         </is>
       </c>
       <c r="C1611" s="3" t="n">
-        <v>-500</v>
+        <v>-1824.26</v>
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>VIAGENS/Passeios</t>
         </is>
       </c>
       <c r="E1611" t="inlineStr">
@@ -71977,17 +71972,17 @@
       </c>
       <c r="G1611" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1611" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1611" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1611" t="inlineStr">
@@ -71998,19 +71993,19 @@
     </row>
     <row r="1612">
       <c r="A1612" s="2" t="n">
-        <v>46383</v>
+        <v>46375</v>
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1612" s="3" t="n">
-        <v>-139</v>
+        <v>-8.99</v>
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1612" t="inlineStr">
@@ -72025,35 +72020,35 @@
       </c>
       <c r="G1612" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1612" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1612" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" s="2" t="n">
-        <v>46383</v>
+        <v>46378</v>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Lata de lixo e outros utensílios domésticos</t>
         </is>
       </c>
       <c r="C1613" s="3" t="n">
-        <v>-102.5</v>
+        <v>-53.66</v>
       </c>
       <c r="D1613" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1613" t="inlineStr">
@@ -72068,12 +72063,17 @@
       </c>
       <c r="G1613" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1613" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1613" t="inlineStr">
@@ -72084,49 +72084,231 @@
     </row>
     <row r="1614">
       <c r="A1614" s="2" t="n">
+        <v>46378</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Casa Aracaju - Materiais para o jardim</t>
+        </is>
+      </c>
+      <c r="C1614" s="3" t="n">
+        <v>-112.07</v>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>Restauração e Manutenção</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
+        </is>
+      </c>
+      <c r="I1614" t="inlineStr">
+        <is>
+          <t>Despesas com imóveis</t>
+        </is>
+      </c>
+      <c r="J1614" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="2" t="n">
+        <v>46380</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+        </is>
+      </c>
+      <c r="C1615" s="3" t="n">
+        <v>-500</v>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>Automóvel/Manutenção</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1615" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
+        </is>
+      </c>
+      <c r="I1615" t="inlineStr">
+        <is>
+          <t>Despesas com Automóvel (Manutenção)</t>
+        </is>
+      </c>
+      <c r="J1615" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="2" t="n">
+        <v>46383</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Troca da bateria do MACBOOK PRO</t>
+        </is>
+      </c>
+      <c r="C1616" s="3" t="n">
+        <v>-102.5</v>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>OUTRAS DESPESAS</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>OUTRAS DESPESAS</t>
+        </is>
+      </c>
+      <c r="I1616" t="inlineStr">
+        <is>
+          <t>Outras Despesas</t>
+        </is>
+      </c>
+      <c r="J1616" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="2" t="n">
+        <v>46383</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Aquisição do celular MOTOROLA G86</t>
+        </is>
+      </c>
+      <c r="C1617" s="3" t="n">
+        <v>-139</v>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>Eletrônicos</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>BENS DURÁVEIS</t>
+        </is>
+      </c>
+      <c r="I1617" t="inlineStr">
+        <is>
+          <t>Investimentos Bens</t>
+        </is>
+      </c>
+      <c r="J1617" t="inlineStr">
+        <is>
+          <t>Investimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="2" t="n">
         <v>46384</v>
       </c>
-      <c r="B1614" t="inlineStr">
+      <c r="B1618" t="inlineStr">
         <is>
           <t>TV SAMSUNG quarto do casal (8 / 8)</t>
         </is>
       </c>
-      <c r="C1614" s="3" t="n">
+      <c r="C1618" s="3" t="n">
         <v>-337.48</v>
       </c>
-      <c r="D1614" t="inlineStr">
+      <c r="D1618" t="inlineStr">
         <is>
           <t>Acessórios</t>
         </is>
       </c>
-      <c r="E1614" t="inlineStr">
-        <is>
-          <t>Cartão BB VISA</t>
-        </is>
-      </c>
-      <c r="F1614" t="inlineStr">
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="G1614" t="inlineStr">
+      <c r="G1618" t="inlineStr">
         <is>
           <t>FAMÍLIA</t>
         </is>
       </c>
-      <c r="I1614" t="inlineStr">
+      <c r="I1618" t="inlineStr">
         <is>
           <t>Despesas com família</t>
         </is>
       </c>
-      <c r="J1614" t="inlineStr">
+      <c r="J1618" t="inlineStr">
         <is>
           <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1614"/>
+  <autoFilter ref="A1:J1618"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Arquivos_Origem/Registros_2026.xlsx
+++ b/Arquivos_Origem/Registros_2026.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transações" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transações'!$A$1:$J$1621</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transações'!$A$1:$J$1628</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1621"/>
+  <dimension ref="A1:J1628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,20 +540,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Combustível para a HILUX</t>
+          <t>Ajuda aos necessitados</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>-230.4</v>
+        <v>-60</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Combustível</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Despesas com Combustível</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ajuda aos necessitados</t>
+          <t>Serviço Apartamento 42 - São Paulo (P 2)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-60</v>
+        <v>-2801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -626,20 +626,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Serviço Apartamento 42 - São Paulo (P 2)</t>
+          <t>Alimentos e Materiais de limpeza</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-2801</v>
+        <v>-924.88</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -669,15 +669,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alimentos e Materiais de limpeza</t>
+          <t>Combustível para a HILUX</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-924.88</v>
+        <v>-230.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Combustível</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com Combustível</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -36283,15 +36283,15 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Estacionamento SHOPPING RIOMAR (Depósito)</t>
         </is>
       </c>
       <c r="C809" s="3" t="n">
-        <v>-38.94</v>
+        <v>-88</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Estacionamento</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -36306,12 +36306,12 @@
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com Estacionamento</t>
         </is>
       </c>
       <c r="J809" t="inlineStr">
@@ -36498,15 +36498,15 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Alimentos</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C814" s="3" t="n">
-        <v>-219.37</v>
+        <v>-38.94</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -36521,12 +36521,12 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J814" t="inlineStr">
@@ -36541,11 +36541,11 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Ovos, frangos e materiais de limpeza</t>
+          <t>Alimentos</t>
         </is>
       </c>
       <c r="C815" s="3" t="n">
-        <v>-167.89</v>
+        <v>-219.37</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -36584,15 +36584,15 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Estacionamento SHOPPING RIOMAR (Depósito)</t>
+          <t>Ovos, frangos e materiais de limpeza</t>
         </is>
       </c>
       <c r="C816" s="3" t="n">
-        <v>-88</v>
+        <v>-167.89</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Estacionamento</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -36607,12 +36607,12 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
         <is>
-          <t>Despesas com Estacionamento</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J816" t="inlineStr">
@@ -36809,20 +36809,20 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Ajuda a Casa do Pobre</t>
+          <t>Café da manhã</t>
         </is>
       </c>
       <c r="C821" s="3" t="n">
-        <v>-30</v>
+        <v>-38.83</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
@@ -36832,12 +36832,12 @@
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
@@ -36852,15 +36852,15 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Juros de Investimento - BB RF Ref DI Cash Pvt</t>
+          <t>Ajuda a Casa do Pobre</t>
         </is>
       </c>
       <c r="C822" s="3" t="n">
-        <v>8704.33</v>
+        <v>-30</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Juros de Investimento</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -36875,22 +36875,17 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H822" t="inlineStr">
-        <is>
-          <t>Financeiras</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -36986,20 +36981,20 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Café da manhã</t>
+          <t>Água mineral</t>
         </is>
       </c>
       <c r="C825" s="3" t="n">
-        <v>-38.83</v>
+        <v>-5</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Carteira</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
@@ -37029,20 +37024,20 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Água mineral</t>
+          <t>Juros de Investimento - BB RF Ref DI Cash Pvt</t>
         </is>
       </c>
       <c r="C826" s="3" t="n">
-        <v>-5</v>
+        <v>8704.33</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Juros de Investimento</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Carteira</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -37052,17 +37047,22 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>Financeiras</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -54637,20 +54637,20 @@
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Lanche com Gracinha</t>
         </is>
       </c>
       <c r="C1222" s="3" t="n">
-        <v>-75000</v>
+        <v>-26.5</v>
       </c>
       <c r="D1222" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1222" t="inlineStr">
@@ -54660,17 +54660,17 @@
       </c>
       <c r="G1222" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1222" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1222" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -54680,20 +54680,20 @@
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>Café da manhã com Gracinha</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1223" s="3" t="n">
-        <v>-42.14</v>
+        <v>-75000</v>
       </c>
       <c r="D1223" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1223" t="inlineStr">
@@ -54703,17 +54703,17 @@
       </c>
       <c r="G1223" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1223" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1223" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -54723,15 +54723,15 @@
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>Ajuda aos necessitados (sacolas de plástico) (1 / 2)</t>
+          <t>Café da manhã com Gracinha</t>
         </is>
       </c>
       <c r="C1224" s="3" t="n">
-        <v>-102.75</v>
+        <v>-42.14</v>
       </c>
       <c r="D1224" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>Padaria</t>
         </is>
       </c>
       <c r="E1224" t="inlineStr">
@@ -54746,12 +54746,12 @@
       </c>
       <c r="G1224" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1224" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1224" t="inlineStr">
@@ -54766,15 +54766,15 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>Lanche com Gracinha</t>
+          <t>Ajuda aos necessitados (sacolas de plástico) (1 / 2)</t>
         </is>
       </c>
       <c r="C1225" s="3" t="n">
-        <v>-26.5</v>
+        <v>-102.75</v>
       </c>
       <c r="D1225" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E1225" t="inlineStr">
@@ -54789,12 +54789,12 @@
       </c>
       <c r="G1225" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I1225" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J1225" t="inlineStr">
@@ -54852,20 +54852,20 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Transferência para a Carteira 2</t>
+          <t>Perfume no Boticário (2 / 10)</t>
         </is>
       </c>
       <c r="C1227" s="3" t="n">
-        <v>-8</v>
+        <v>-8.99</v>
       </c>
       <c r="D1227" t="inlineStr">
         <is>
-          <t>Transferência entre Contas</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1227" t="inlineStr">
@@ -54875,17 +54875,17 @@
       </c>
       <c r="G1227" t="inlineStr">
         <is>
-          <t>ESPECIAIS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1227" t="inlineStr">
         <is>
-          <t>Transferência entre Contas</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1227" t="inlineStr">
         <is>
-          <t>Transferência entre Contas</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -54895,20 +54895,20 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>Salada de Frutas</t>
+          <t>Transferência para a Carteira 2</t>
         </is>
       </c>
       <c r="C1228" s="3" t="n">
-        <v>-28</v>
+        <v>-8</v>
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Transferência entre Contas</t>
         </is>
       </c>
       <c r="E1228" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1228" t="inlineStr">
@@ -54918,17 +54918,17 @@
       </c>
       <c r="G1228" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>ESPECIAIS</t>
         </is>
       </c>
       <c r="I1228" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Transferência entre Contas</t>
         </is>
       </c>
       <c r="J1228" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Transferência entre Contas</t>
         </is>
       </c>
     </row>
@@ -54938,15 +54938,15 @@
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Perfume no Boticário (2 / 10)</t>
+          <t>Almoço com Gracinha</t>
         </is>
       </c>
       <c r="C1229" s="3" t="n">
-        <v>-8.99</v>
+        <v>-104.69</v>
       </c>
       <c r="D1229" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1229" t="inlineStr">
@@ -54961,12 +54961,12 @@
       </c>
       <c r="G1229" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1229" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1229" t="inlineStr">
@@ -55158,15 +55158,15 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>Almoço com Gracinha</t>
+          <t>Salada de Frutas</t>
         </is>
       </c>
       <c r="C1234" s="3" t="n">
-        <v>-104.69</v>
+        <v>-28</v>
       </c>
       <c r="D1234" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1234" t="inlineStr">
@@ -63603,7 +63603,7 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>Lanche com Gracinha (-11,20 EURO)</t>
+          <t>Lanche com Gracinha (-7,70 EURO) - (Saldo 129,45 EURO)</t>
         </is>
       </c>
       <c r="C1424" s="3" t="n">
@@ -63689,7 +63689,7 @@
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Protetor de pele para Isadora (-29,90 EURO)</t>
+          <t>Lanche com Gracinha (-11,20 EURO)</t>
         </is>
       </c>
       <c r="C1426" s="3" t="n">
@@ -63697,7 +63697,7 @@
       </c>
       <c r="D1426" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1426" t="inlineStr">
@@ -63712,12 +63712,12 @@
       </c>
       <c r="G1426" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1426" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1426" t="inlineStr">
@@ -63732,7 +63732,7 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>Almoço com Gracinha (-23,00 EURO)</t>
+          <t>Protetor de pele para Isadora (-29,90 EURO)</t>
         </is>
       </c>
       <c r="C1427" s="3" t="n">
@@ -63740,7 +63740,7 @@
       </c>
       <c r="D1427" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1427" t="inlineStr">
@@ -63755,12 +63755,12 @@
       </c>
       <c r="G1427" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1427" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1427" t="inlineStr">
@@ -63775,7 +63775,7 @@
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Lanche com Gracinha (-7,70 EURO) - (Saldo 129,45 EURO)</t>
+          <t>Almoço com Gracinha (-23,00 EURO)</t>
         </is>
       </c>
       <c r="C1428" s="3" t="n">
@@ -63783,7 +63783,7 @@
       </c>
       <c r="D1428" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1428" t="inlineStr">
@@ -63861,35 +63861,40 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Lanche com Gracinha</t>
+          <t>Casa Aracaju - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1430" s="3" t="n">
-        <v>-42.7</v>
+        <v>-213.57</v>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1430" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1430" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1430" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1430" t="inlineStr">
@@ -63952,40 +63957,35 @@
       </c>
       <c r="B1432" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Energia Elétrica</t>
+          <t>Lanche com Gracinha</t>
         </is>
       </c>
       <c r="C1432" s="3" t="n">
-        <v>-213.57</v>
+        <v>-42.7</v>
       </c>
       <c r="D1432" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1432" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1432" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1432" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1432" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1432" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1432" t="inlineStr">
@@ -64000,40 +64000,35 @@
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Apt. Aju. - Condomínio</t>
+          <t>Almoço com Gracinha</t>
         </is>
       </c>
       <c r="C1433" s="3" t="n">
-        <v>-822.89</v>
+        <v>-163.07</v>
       </c>
       <c r="D1433" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1433" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1433" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1433" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1433" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1433" t="inlineStr">
@@ -64091,35 +64086,40 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Almoço com Gracinha</t>
+          <t>Apt. Aju. - Condomínio</t>
         </is>
       </c>
       <c r="C1435" s="3" t="n">
-        <v>-163.07</v>
+        <v>-822.89</v>
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1435" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1435" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1435" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1435" t="inlineStr">
@@ -65939,40 +65939,40 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
+          <t>Aplicação PGBL BRASILPREV - ACMD (10 / 12)</t>
         </is>
       </c>
       <c r="C1476" s="3" t="n">
-        <v>-58.07</v>
+        <v>-218.18</v>
       </c>
       <c r="D1476" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>BRASILPREV</t>
         </is>
       </c>
       <c r="E1476" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1476" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1476" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1476" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1476" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -66030,15 +66030,15 @@
       </c>
       <c r="B1478" t="inlineStr">
         <is>
-          <t>Jantar com Gracinha</t>
+          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
         </is>
       </c>
       <c r="C1478" s="3" t="n">
-        <v>-38.19</v>
+        <v>-58.07</v>
       </c>
       <c r="D1478" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1478" t="inlineStr">
@@ -66053,17 +66053,17 @@
       </c>
       <c r="G1478" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1478" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1478" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
@@ -66073,40 +66073,40 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Aplicação PGBL BRASILPREV - ACMD (10 / 12)</t>
+          <t>Jantar com Gracinha</t>
         </is>
       </c>
       <c r="C1479" s="3" t="n">
-        <v>-218.18</v>
+        <v>-38.19</v>
       </c>
       <c r="D1479" t="inlineStr">
         <is>
-          <t>BRASILPREV</t>
+          <t>Padaria</t>
         </is>
       </c>
       <c r="E1479" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1479" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1479" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1479" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1479" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68000,35 +68000,35 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Celulares - VIVO</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1523" s="3" t="n">
-        <v>-359.89</v>
+        <v>-19.99</v>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1523" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1523" t="inlineStr">
@@ -68043,15 +68043,15 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Produtos Químicos para limpeza de piso externo</t>
         </is>
       </c>
       <c r="C1524" s="3" t="n">
-        <v>-8.99</v>
+        <v>-73.5</v>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1524" t="inlineStr">
@@ -68066,12 +68066,12 @@
       </c>
       <c r="G1524" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1524" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1524" t="inlineStr">
@@ -68086,35 +68086,35 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Celulares - VIVO</t>
         </is>
       </c>
       <c r="C1525" s="3" t="n">
-        <v>-19.99</v>
+        <v>-359.89</v>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Celular</t>
         </is>
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1525" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1525" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1525" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1525" t="inlineStr">
@@ -68129,35 +68129,35 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Produtos Químicos para limpeza de piso externo</t>
+          <t>Protetor Auricular (com abafador de ruído</t>
         </is>
       </c>
       <c r="C1526" s="3" t="n">
-        <v>-73.5</v>
+        <v>-51.99</v>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1526" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1526" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1526" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1526" t="inlineStr">
@@ -68172,25 +68172,25 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Protetor Auricular (com abafador de ruído</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1527" s="3" t="n">
-        <v>-51.99</v>
+        <v>-8.99</v>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1527" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1527" t="inlineStr">
@@ -68258,20 +68258,20 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Pagamento DAE (09.2026) - Ivonilde</t>
+          <t>Sacos para os alimentos dos necessitados (1 / 2)</t>
         </is>
       </c>
       <c r="C1529" s="3" t="n">
-        <v>-445.76</v>
+        <v>-72</v>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>Encargos Empregados</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1529" t="inlineStr">
@@ -68281,12 +68281,12 @@
       </c>
       <c r="G1529" t="inlineStr">
         <is>
-          <t>EMPREGADOS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1529" t="inlineStr">
         <is>
-          <t>Despesas com empregados</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1529" t="inlineStr">
@@ -68301,20 +68301,20 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Resgate de Investimento - BB RF DEB INC PVT</t>
+          <t>Materiais de limpeza (1 / 2)</t>
         </is>
       </c>
       <c r="C1530" s="3" t="n">
-        <v>100000</v>
+        <v>-110.2</v>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1530" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1530" t="inlineStr">
@@ -68324,17 +68324,17 @@
       </c>
       <c r="G1530" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1530" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1530" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68344,20 +68344,20 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Materiais de limpeza (1 / 2)</t>
+          <t>Pagamento DAE (09.2026) - Ivonilde</t>
         </is>
       </c>
       <c r="C1531" s="3" t="n">
-        <v>-110.2</v>
+        <v>-445.76</v>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Encargos Empregados</t>
         </is>
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1531" t="inlineStr">
@@ -68367,12 +68367,12 @@
       </c>
       <c r="G1531" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>EMPREGADOS</t>
         </is>
       </c>
       <c r="I1531" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com empregados</t>
         </is>
       </c>
       <c r="J1531" t="inlineStr">
@@ -68387,20 +68387,20 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Sacos para os alimentos dos necessitados (1 / 2)</t>
+          <t>Resgate de Investimento - BB RF DEB INC PVT</t>
         </is>
       </c>
       <c r="C1532" s="3" t="n">
-        <v>-72</v>
+        <v>100000</v>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1532" t="inlineStr">
@@ -68410,17 +68410,17 @@
       </c>
       <c r="G1532" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1532" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1532" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -68430,15 +68430,15 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Remédios para Isadora</t>
+          <t>Devolução do valor do equipamento da ARZOPA</t>
         </is>
       </c>
       <c r="C1533" s="3" t="n">
-        <v>-113.87</v>
+        <v>159.47</v>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Reembolso</t>
         </is>
       </c>
       <c r="E1533" t="inlineStr">
@@ -68448,22 +68448,27 @@
       </c>
       <c r="F1533" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1533" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>Outras</t>
         </is>
       </c>
       <c r="I1533" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1533" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
@@ -68473,15 +68478,15 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (02)</t>
+          <t>Remédios para Isadora</t>
         </is>
       </c>
       <c r="C1534" s="3" t="n">
-        <v>-1063.47</v>
+        <v>-113.87</v>
       </c>
       <c r="D1534" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1534" t="inlineStr">
@@ -68491,22 +68496,17 @@
       </c>
       <c r="F1534" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1534" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1534" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1534" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1534" t="inlineStr">
@@ -68521,15 +68521,15 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Equipamento para interligar no ARZOPA</t>
         </is>
       </c>
       <c r="C1535" s="3" t="n">
-        <v>-100000</v>
+        <v>-159.47</v>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1535" t="inlineStr">
@@ -68544,17 +68544,17 @@
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1535" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1535" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
@@ -68564,40 +68564,40 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Café da manhã com Gracinha</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1536" s="3" t="n">
-        <v>-39.75</v>
+        <v>-100000</v>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1536" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1536" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1536" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1536" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -68607,15 +68607,15 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Aluguel de terno para Nicholas (1 / 2)</t>
+          <t>Café da manhã com Gracinha</t>
         </is>
       </c>
       <c r="C1537" s="3" t="n">
-        <v>-175</v>
+        <v>-39.75</v>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Padaria</t>
         </is>
       </c>
       <c r="E1537" t="inlineStr">
@@ -68630,12 +68630,12 @@
       </c>
       <c r="G1537" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1537" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1537" t="inlineStr">
@@ -68650,45 +68650,40 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Devolução do valor da compra dia 08/10/2026</t>
+          <t>Aluguel de terno para Nicholas (1 / 2)</t>
         </is>
       </c>
       <c r="C1538" s="3" t="n">
-        <v>228.92</v>
+        <v>-175</v>
       </c>
       <c r="D1538" t="inlineStr">
         <is>
-          <t>Reembolso</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1538" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H1538" t="inlineStr">
-        <is>
-          <t>Outras</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1538" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1538" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68698,15 +68693,15 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Devolução do valor do equipamento da ARZOPA</t>
+          <t>Apt. SP. - Condomínio (02)</t>
         </is>
       </c>
       <c r="C1539" s="3" t="n">
-        <v>159.47</v>
+        <v>-1063.47</v>
       </c>
       <c r="D1539" t="inlineStr">
         <is>
-          <t>Reembolso</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1539" t="inlineStr">
@@ -68721,22 +68716,22 @@
       </c>
       <c r="G1539" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1539" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1539" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1539" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68746,15 +68741,15 @@
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Equipamento para interligar no ARZOPA</t>
+          <t>Devolução do valor da compra dia 08/10/2026</t>
         </is>
       </c>
       <c r="C1540" s="3" t="n">
-        <v>-159.47</v>
+        <v>228.92</v>
       </c>
       <c r="D1540" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Reembolso</t>
         </is>
       </c>
       <c r="E1540" t="inlineStr">
@@ -68769,17 +68764,22 @@
       </c>
       <c r="G1540" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>Outras</t>
         </is>
       </c>
       <c r="I1540" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1540" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
@@ -68789,40 +68789,35 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Água de Côco</t>
         </is>
       </c>
       <c r="C1541" s="3" t="n">
-        <v>-112.07</v>
+        <v>-10</v>
       </c>
       <c r="D1541" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1541" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1541" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1541" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1541" t="inlineStr">
@@ -68837,11 +68832,11 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Casa Aracaju - Materiais para o jardim</t>
         </is>
       </c>
       <c r="C1542" s="3" t="n">
-        <v>-53.66</v>
+        <v>-112.07</v>
       </c>
       <c r="D1542" t="inlineStr">
         <is>
@@ -68855,7 +68850,7 @@
       </c>
       <c r="F1542" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1542" t="inlineStr">
@@ -68881,49 +68876,49 @@
     </row>
     <row r="1543">
       <c r="A1543" s="2" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Benefício PETROS</t>
+          <t>Lata de lixo e outros utensílios domésticos</t>
         </is>
       </c>
       <c r="C1543" s="3" t="n">
-        <v>10524.94</v>
+        <v>-53.66</v>
       </c>
       <c r="D1543" t="inlineStr">
         <is>
-          <t>Benefícios Aposentadoria</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1543" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1543" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1543" t="inlineStr">
         <is>
-          <t>Trabalho e Benefícios</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1543" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1543" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68933,15 +68928,15 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Benefício PETROS II</t>
+          <t>Água de côco e Suco de Laranja</t>
         </is>
       </c>
       <c r="C1544" s="3" t="n">
-        <v>4694.46</v>
+        <v>-40</v>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
-          <t>Benefícios Aposentadoria</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1544" t="inlineStr">
@@ -68951,27 +68946,22 @@
       </c>
       <c r="F1544" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1544" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H1544" t="inlineStr">
-        <is>
-          <t>Trabalho e Benefícios</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1544" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1544" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68981,11 +68971,11 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Benefício INSS</t>
+          <t>Benefício PETROS II</t>
         </is>
       </c>
       <c r="C1545" s="3" t="n">
-        <v>6334.53</v>
+        <v>4694.46</v>
       </c>
       <c r="D1545" t="inlineStr">
         <is>
@@ -69025,24 +69015,24 @@
     </row>
     <row r="1546">
       <c r="A1546" s="2" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Benefício INSS</t>
         </is>
       </c>
       <c r="C1546" s="3" t="n">
-        <v>-500</v>
+        <v>6334.53</v>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Benefícios Aposentadoria</t>
         </is>
       </c>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1546" t="inlineStr">
@@ -69052,40 +69042,40 @@
       </c>
       <c r="G1546" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>RECEITAS</t>
         </is>
       </c>
       <c r="H1546" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>Trabalho e Benefícios</t>
         </is>
       </c>
       <c r="I1546" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1546" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" s="2" t="n">
-        <v>46320</v>
+        <v>46318</v>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Pagamento "DUO GOURMET"</t>
+          <t>Benefício PETROS</t>
         </is>
       </c>
       <c r="C1547" s="3" t="n">
-        <v>-45</v>
+        <v>10524.94</v>
       </c>
       <c r="D1547" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Benefícios Aposentadoria</t>
         </is>
       </c>
       <c r="E1547" t="inlineStr">
@@ -69100,40 +69090,45 @@
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1547" t="inlineStr">
+        <is>
+          <t>Trabalho e Benefícios</t>
         </is>
       </c>
       <c r="I1547" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1547" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" s="2" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Link de Internet - CLARO</t>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
         </is>
       </c>
       <c r="C1548" s="3" t="n">
-        <v>-267.06</v>
+        <v>-500</v>
       </c>
       <c r="D1548" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1548" t="inlineStr">
@@ -69143,12 +69138,17 @@
       </c>
       <c r="G1548" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1548" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1548" t="inlineStr">
@@ -69207,24 +69207,24 @@
     </row>
     <row r="1550">
       <c r="A1550" s="2" t="n">
-        <v>46322</v>
+        <v>46320</v>
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Pagamento "DUO GOURMET"</t>
         </is>
       </c>
       <c r="C1550" s="3" t="n">
-        <v>-102.5</v>
+        <v>-45</v>
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1550" t="inlineStr">
@@ -69234,12 +69234,12 @@
       </c>
       <c r="G1550" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1550" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1550" t="inlineStr">
@@ -69250,24 +69250,24 @@
     </row>
     <row r="1551">
       <c r="A1551" s="2" t="n">
-        <v>46322</v>
+        <v>46320</v>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Link de Internet - CLARO</t>
         </is>
       </c>
       <c r="C1551" s="3" t="n">
-        <v>-139</v>
+        <v>-267.06</v>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1551" t="inlineStr">
@@ -69277,40 +69277,40 @@
       </c>
       <c r="G1551" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1551" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1551" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" s="2" t="n">
-        <v>46323</v>
+        <v>46320</v>
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Apt. SP. - Gás Natural</t>
+          <t>Salada de frutas</t>
         </is>
       </c>
       <c r="C1552" s="3" t="n">
-        <v>-63.96</v>
+        <v>-29.15</v>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>Gás</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1552" t="inlineStr">
@@ -69320,17 +69320,12 @@
       </c>
       <c r="G1552" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1552" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1552" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1552" t="inlineStr">
@@ -69341,24 +69336,24 @@
     </row>
     <row r="1553">
       <c r="A1553" s="2" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>TV SAMSUNG quarto do casal (6 / 8)</t>
+          <t>Apt.AJU. - Investimento Cozinha</t>
         </is>
       </c>
       <c r="C1553" s="3" t="n">
-        <v>-337.49</v>
+        <v>-1500</v>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1553" t="inlineStr">
@@ -69368,40 +69363,40 @@
       </c>
       <c r="G1553" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1553" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1553" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" s="2" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Água e Esgoto</t>
+          <t>Aquisição do celular MOTOROLA G86</t>
         </is>
       </c>
       <c r="C1554" s="3" t="n">
-        <v>-108.5</v>
+        <v>-139</v>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>Água e Esgoto</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1554" t="inlineStr">
@@ -69411,45 +69406,40 @@
       </c>
       <c r="G1554" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1554" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1554" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1554" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" s="2" t="n">
-        <v>46327</v>
+        <v>46322</v>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Cemitério Colina da Saudade 2026</t>
+          <t>Troca da bateria do MACBOOK PRO</t>
         </is>
       </c>
       <c r="C1555" s="3" t="n">
-        <v>-600</v>
+        <v>-102.5</v>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1555" t="inlineStr">
@@ -69459,12 +69449,12 @@
       </c>
       <c r="G1555" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I1555" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J1555" t="inlineStr">
@@ -69475,24 +69465,24 @@
     </row>
     <row r="1556">
       <c r="A1556" s="2" t="n">
-        <v>46327</v>
+        <v>46322</v>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Seguro Apt Aracaju - Parcelas 3</t>
+          <t>Combustível para RANGER XLT</t>
         </is>
       </c>
       <c r="C1556" s="3" t="n">
-        <v>-52.85</v>
+        <v>-364.5</v>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Combustível</t>
         </is>
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1556" t="inlineStr">
@@ -69502,12 +69492,12 @@
       </c>
       <c r="G1556" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I1556" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com Combustível</t>
         </is>
       </c>
       <c r="J1556" t="inlineStr">
@@ -69518,24 +69508,24 @@
     </row>
     <row r="1557">
       <c r="A1557" s="2" t="n">
-        <v>46328</v>
+        <v>46323</v>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Seguro de Itens Pessoais</t>
+          <t>TV SAMSUNG quarto do casal (6 / 8)</t>
         </is>
       </c>
       <c r="C1557" s="3" t="n">
-        <v>-9.9</v>
+        <v>-337.49</v>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -69545,12 +69535,12 @@
       </c>
       <c r="G1557" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1557" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1557" t="inlineStr">
@@ -69561,19 +69551,19 @@
     </row>
     <row r="1558">
       <c r="A1558" s="2" t="n">
-        <v>46329</v>
+        <v>46323</v>
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>Apt. Aju. - Energia Elétrica</t>
+          <t>Estacionamento</t>
         </is>
       </c>
       <c r="C1558" s="3" t="n">
-        <v>-169.78</v>
+        <v>-5</v>
       </c>
       <c r="D1558" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Estacionamento</t>
         </is>
       </c>
       <c r="E1558" t="inlineStr">
@@ -69583,22 +69573,17 @@
       </c>
       <c r="F1558" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1558" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1558" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I1558" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Estacionamento</t>
         </is>
       </c>
       <c r="J1558" t="inlineStr">
@@ -69609,19 +69594,19 @@
     </row>
     <row r="1559">
       <c r="A1559" s="2" t="n">
-        <v>46329</v>
+        <v>46323</v>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
+          <t>Apt. SP. - Gás Natural</t>
         </is>
       </c>
       <c r="C1559" s="3" t="n">
-        <v>200000</v>
+        <v>-63.96</v>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Gás</t>
         </is>
       </c>
       <c r="E1559" t="inlineStr">
@@ -69636,40 +69621,45 @@
       </c>
       <c r="G1559" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1559" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1559" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1559" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" s="2" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Filtro para a COIFA - CONSUL</t>
+          <t>Casa Aracaju - Água e Esgoto</t>
         </is>
       </c>
       <c r="C1560" s="3" t="n">
-        <v>-138.27</v>
+        <v>-108.5</v>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Água e Esgoto</t>
         </is>
       </c>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>Cartão BB ELO</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1560" t="inlineStr">
@@ -69684,7 +69674,7 @@
       </c>
       <c r="H1560" t="inlineStr">
         <is>
-          <t>Manutenção e encargos</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1560" t="inlineStr">
@@ -69700,24 +69690,24 @@
     </row>
     <row r="1561">
       <c r="A1561" s="2" t="n">
-        <v>46332</v>
+        <v>46327</v>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Película para RANGER XLT</t>
+          <t>Seguro Apt Aracaju - Parcelas 3</t>
         </is>
       </c>
       <c r="C1561" s="3" t="n">
-        <v>-100</v>
+        <v>-52.85</v>
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1561" t="inlineStr">
@@ -69727,17 +69717,12 @@
       </c>
       <c r="G1561" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1561" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1561" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1561" t="inlineStr">
@@ -69748,19 +69733,19 @@
     </row>
     <row r="1562">
       <c r="A1562" s="2" t="n">
-        <v>46332</v>
+        <v>46327</v>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
+          <t>Cemitério Colina da Saudade 2026</t>
         </is>
       </c>
       <c r="C1562" s="3" t="n">
-        <v>-17600</v>
+        <v>-600</v>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1562" t="inlineStr">
@@ -69775,35 +69760,35 @@
       </c>
       <c r="G1562" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1562" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1562" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" s="2" t="n">
-        <v>46333</v>
+        <v>46328</v>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (01)</t>
+          <t>Seguro de Itens Pessoais</t>
         </is>
       </c>
       <c r="C1563" s="3" t="n">
-        <v>-1429.33</v>
+        <v>-9.9</v>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Equipamentos Eletrônicos</t>
         </is>
       </c>
       <c r="E1563" t="inlineStr">
@@ -69818,17 +69803,12 @@
       </c>
       <c r="G1563" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1563" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1563" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1563" t="inlineStr">
@@ -69839,24 +69819,24 @@
     </row>
     <row r="1564">
       <c r="A1564" s="2" t="n">
-        <v>46334</v>
+        <v>46329</v>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
+          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
         </is>
       </c>
       <c r="C1564" s="3" t="n">
-        <v>-540.29</v>
+        <v>200000</v>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1564" t="inlineStr">
@@ -69866,45 +69846,40 @@
       </c>
       <c r="G1564" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1564" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1564" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1564" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" s="2" t="n">
-        <v>46334</v>
+        <v>46329</v>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
+          <t>Apt. Aju. - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1565" s="3" t="n">
-        <v>-124.64</v>
+        <v>-169.78</v>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1565" t="inlineStr">
@@ -69914,17 +69889,17 @@
       </c>
       <c r="G1565" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1565" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1565" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1565" t="inlineStr">
@@ -69935,24 +69910,24 @@
     </row>
     <row r="1566">
       <c r="A1566" s="2" t="n">
-        <v>46334</v>
+        <v>46329</v>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Sapato para ACMD</t>
+          <t>Casa Aracaju - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1566" s="3" t="n">
-        <v>-121.6</v>
+        <v>-182</v>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1566" t="inlineStr">
@@ -69962,12 +69937,17 @@
       </c>
       <c r="G1566" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1566" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1566" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1566" t="inlineStr">
@@ -69978,24 +69958,24 @@
     </row>
     <row r="1567">
       <c r="A1567" s="2" t="n">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
+          <t>Película para RANGER XLT</t>
         </is>
       </c>
       <c r="C1567" s="3" t="n">
-        <v>300000</v>
+        <v>-100</v>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1567" t="inlineStr">
@@ -70005,35 +69985,40 @@
       </c>
       <c r="G1567" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1567" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1567" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1567" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" s="2" t="n">
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Condomínio</t>
+          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
         </is>
       </c>
       <c r="C1568" s="3" t="n">
-        <v>-1650</v>
+        <v>-17600</v>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1568" t="inlineStr">
@@ -70048,45 +70033,40 @@
       </c>
       <c r="G1568" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1568" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1568" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1568" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" s="2" t="n">
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Filtro para a COIFA - CONSUL</t>
         </is>
       </c>
       <c r="C1569" s="3" t="n">
-        <v>-300000</v>
+        <v>-138.27</v>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB ELO</t>
         </is>
       </c>
       <c r="F1569" t="inlineStr">
@@ -70096,35 +70076,40 @@
       </c>
       <c r="G1569" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1569" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1569" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" s="2" t="n">
-        <v>46336</v>
+        <v>46333</v>
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Taxa Extra (9 de 12 )</t>
+          <t>Apt. SP. - Condomínio (01)</t>
         </is>
       </c>
       <c r="C1570" s="3" t="n">
-        <v>-500</v>
+        <v>-1429.33</v>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1570" t="inlineStr">
@@ -70139,40 +70124,45 @@
       </c>
       <c r="G1570" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1570" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1570" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" s="2" t="n">
-        <v>46336</v>
+        <v>46334</v>
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Presentes comprados por Gracinha (2026.10.14)</t>
+          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
         </is>
       </c>
       <c r="C1571" s="3" t="n">
-        <v>-134.38</v>
+        <v>-540.29</v>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1571" t="inlineStr">
@@ -70182,12 +70172,17 @@
       </c>
       <c r="G1571" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1571" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1571" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1571" t="inlineStr">
@@ -70198,24 +70193,24 @@
     </row>
     <row r="1572">
       <c r="A1572" s="2" t="n">
-        <v>46336</v>
+        <v>46334</v>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>Aplicação PGBL BRASILPREV - ACMD</t>
+          <t>Sapato para ACMD</t>
         </is>
       </c>
       <c r="C1572" s="3" t="n">
-        <v>-209.34</v>
+        <v>-121.6</v>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>BRASILPREV</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1572" t="inlineStr">
@@ -70225,31 +70220,31 @@
       </c>
       <c r="G1572" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1572" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1572" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" s="2" t="n">
-        <v>46336</v>
+        <v>46334</v>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>Hotel Stela Maris - Salvador</t>
+          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
         </is>
       </c>
       <c r="C1573" s="3" t="n">
-        <v>-69.37</v>
+        <v>-124.64</v>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
@@ -70258,7 +70253,7 @@
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1573" t="inlineStr">
@@ -70289,19 +70284,19 @@
     </row>
     <row r="1574">
       <c r="A1574" s="2" t="n">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>Plano OSAF - Serviços Funerários</t>
+          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
         </is>
       </c>
       <c r="C1574" s="3" t="n">
-        <v>-82.64</v>
+        <v>300000</v>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1574" t="inlineStr">
@@ -70316,17 +70311,17 @@
       </c>
       <c r="G1574" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1574" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1574" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -70336,15 +70331,15 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>Mensalidade da hidroginástica (10 / 11)</t>
+          <t>Casa Aracaju - Condomínio</t>
         </is>
       </c>
       <c r="C1575" s="3" t="n">
-        <v>-88</v>
+        <v>-1650</v>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1575" t="inlineStr">
@@ -70359,12 +70354,17 @@
       </c>
       <c r="G1575" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1575" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1575" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1575" t="inlineStr">
@@ -70375,15 +70375,15 @@
     </row>
     <row r="1576">
       <c r="A1576" s="2" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
+          <t>Casa Aracaju - Taxa Extra (9 de 12 )</t>
         </is>
       </c>
       <c r="C1576" s="3" t="n">
-        <v>-1818.04</v>
+        <v>-500</v>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
@@ -70392,7 +70392,7 @@
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1576" t="inlineStr">
@@ -70418,24 +70418,24 @@
     </row>
     <row r="1577">
       <c r="A1577" s="2" t="n">
-        <v>46338</v>
+        <v>46336</v>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Aluguel do terno para o casamento de João Paulo</t>
+          <t>Mensalidade da hidroginástica (10 / 11)</t>
         </is>
       </c>
       <c r="C1577" s="3" t="n">
-        <v>-116.67</v>
+        <v>-88</v>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1577" t="inlineStr">
@@ -70461,24 +70461,24 @@
     </row>
     <row r="1578">
       <c r="A1578" s="2" t="n">
-        <v>46339</v>
+        <v>46336</v>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
+          <t>Plano OSAF - Serviços Funerários</t>
         </is>
       </c>
       <c r="C1578" s="3" t="n">
-        <v>-58.07</v>
+        <v>-82.64</v>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1578" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1578" t="inlineStr">
@@ -70488,40 +70488,40 @@
       </c>
       <c r="G1578" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1578" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1578" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" s="2" t="n">
-        <v>46339</v>
+        <v>46336</v>
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Seguro da Hilux SW4</t>
+          <t>Hotel Stela Maris - Salvador</t>
         </is>
       </c>
       <c r="C1579" s="3" t="n">
-        <v>-233.11</v>
+        <v>-69.37</v>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1579" t="inlineStr">
@@ -70531,17 +70531,17 @@
       </c>
       <c r="G1579" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1579" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1579" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1579" t="inlineStr">
@@ -70552,24 +70552,24 @@
     </row>
     <row r="1580">
       <c r="A1580" s="2" t="n">
-        <v>46339</v>
+        <v>46336</v>
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
+          <t>Aplicação PGBL BRASILPREV - ACMD</t>
         </is>
       </c>
       <c r="C1580" s="3" t="n">
-        <v>-93.89</v>
+        <v>-209.34</v>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>BRASILPREV</t>
         </is>
       </c>
       <c r="E1580" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1580" t="inlineStr">
@@ -70579,45 +70579,40 @@
       </c>
       <c r="G1580" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1580" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1580" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1580" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" s="2" t="n">
-        <v>46341</v>
+        <v>46336</v>
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Presentes comprados por Gracinha (2026.10.14)</t>
         </is>
       </c>
       <c r="C1581" s="3" t="n">
-        <v>-52.83</v>
+        <v>-134.38</v>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1581" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1581" t="inlineStr">
@@ -70627,12 +70622,12 @@
       </c>
       <c r="G1581" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1581" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1581" t="inlineStr">
@@ -70643,24 +70638,24 @@
     </row>
     <row r="1582">
       <c r="A1582" s="2" t="n">
-        <v>46341</v>
+        <v>46336</v>
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Pagamento Clube SMILES</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1582" s="3" t="n">
-        <v>-46</v>
+        <v>-300000</v>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1582" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1582" t="inlineStr">
@@ -70670,40 +70665,35 @@
       </c>
       <c r="G1582" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1582" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1582" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1582" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" s="2" t="n">
-        <v>46342</v>
+        <v>46337</v>
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Transporte Terrestre, Hoteis e Excursão</t>
+          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
         </is>
       </c>
       <c r="C1583" s="3" t="n">
-        <v>-1824.26</v>
+        <v>-1818.04</v>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>VIAGENS/Passeios</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1583" t="inlineStr">
@@ -70718,40 +70708,35 @@
       </c>
       <c r="G1583" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1583" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1583" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1583" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" s="2" t="n">
-        <v>46342</v>
+        <v>46338</v>
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Academia ACMD</t>
+          <t>Aluguel do terno para o casamento de João Paulo</t>
         </is>
       </c>
       <c r="C1584" s="3" t="n">
-        <v>-448.35</v>
+        <v>-116.67</v>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1584" t="inlineStr">
@@ -70782,19 +70767,19 @@
     </row>
     <row r="1585">
       <c r="A1585" s="2" t="n">
-        <v>46345</v>
+        <v>46339</v>
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
         </is>
       </c>
       <c r="C1585" s="3" t="n">
-        <v>-8.99</v>
+        <v>-58.07</v>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1585" t="inlineStr">
@@ -70809,35 +70794,35 @@
       </c>
       <c r="G1585" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1585" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1585" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" s="2" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Materiais de limpeza (2 / 2)</t>
+          <t>Seguro da Hilux SW4</t>
         </is>
       </c>
       <c r="C1586" s="3" t="n">
-        <v>-110.2</v>
+        <v>-233.11</v>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1586" t="inlineStr">
@@ -70852,12 +70837,17 @@
       </c>
       <c r="G1586" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1586" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1586" t="inlineStr">
@@ -70868,19 +70858,19 @@
     </row>
     <row r="1587">
       <c r="A1587" s="2" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Sacos para os alimentos dos necessitados (2 / 2)</t>
+          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
         </is>
       </c>
       <c r="C1587" s="3" t="n">
-        <v>-72</v>
+        <v>-93.89</v>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1587" t="inlineStr">
@@ -70895,12 +70885,17 @@
       </c>
       <c r="G1587" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1587" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1587" t="inlineStr">
@@ -70911,19 +70906,19 @@
     </row>
     <row r="1588">
       <c r="A1588" s="2" t="n">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Aluguel de terno para Nicholas (2 / 2)</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1588" s="3" t="n">
-        <v>-175</v>
+        <v>-52.83</v>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1588" t="inlineStr">
@@ -70938,12 +70933,12 @@
       </c>
       <c r="G1588" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1588" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1588" t="inlineStr">
@@ -70954,24 +70949,24 @@
     </row>
     <row r="1589">
       <c r="A1589" s="2" t="n">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (02)</t>
+          <t>Pagamento Clube SMILES</t>
         </is>
       </c>
       <c r="C1589" s="3" t="n">
-        <v>-1063.47</v>
+        <v>-46</v>
       </c>
       <c r="D1589" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1589" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1589" t="inlineStr">
@@ -70981,17 +70976,17 @@
       </c>
       <c r="G1589" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1589" t="inlineStr">
         <is>
-          <t>Contas da casa</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1589" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1589" t="inlineStr">
@@ -71002,19 +70997,19 @@
     </row>
     <row r="1590">
       <c r="A1590" s="2" t="n">
-        <v>46348</v>
+        <v>46342</v>
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Transporte Terrestre, Hoteis e Excursão</t>
         </is>
       </c>
       <c r="C1590" s="3" t="n">
-        <v>-112.07</v>
+        <v>-1824.26</v>
       </c>
       <c r="D1590" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>VIAGENS/Passeios</t>
         </is>
       </c>
       <c r="E1590" t="inlineStr">
@@ -71029,17 +71024,17 @@
       </c>
       <c r="G1590" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1590" t="inlineStr">
         <is>
-          <t>Manutenção e encargos</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1590" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1590" t="inlineStr">
@@ -71050,19 +71045,19 @@
     </row>
     <row r="1591">
       <c r="A1591" s="2" t="n">
-        <v>46348</v>
+        <v>46342</v>
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Academia ACMD</t>
         </is>
       </c>
       <c r="C1591" s="3" t="n">
-        <v>-53.66</v>
+        <v>-448.35</v>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1591" t="inlineStr">
@@ -71077,17 +71072,12 @@
       </c>
       <c r="G1591" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1591" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1591" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1591" t="inlineStr">
@@ -71098,19 +71088,19 @@
     </row>
     <row r="1592">
       <c r="A1592" s="2" t="n">
-        <v>46350</v>
+        <v>46345</v>
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1592" s="3" t="n">
-        <v>-500</v>
+        <v>-8.99</v>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1592" t="inlineStr">
@@ -71125,17 +71115,12 @@
       </c>
       <c r="G1592" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1592" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1592" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1592" t="inlineStr">
@@ -71146,24 +71131,24 @@
     </row>
     <row r="1593">
       <c r="A1593" s="2" t="n">
-        <v>46351</v>
+        <v>46346</v>
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>Pagamento "DUO GOURMET"</t>
+          <t>Materiais de limpeza (2 / 2)</t>
         </is>
       </c>
       <c r="C1593" s="3" t="n">
-        <v>-45</v>
+        <v>-110.2</v>
       </c>
       <c r="D1593" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1593" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1593" t="inlineStr">
@@ -71189,19 +71174,19 @@
     </row>
     <row r="1594">
       <c r="A1594" s="2" t="n">
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Sacos para os alimentos dos necessitados (2 / 2)</t>
         </is>
       </c>
       <c r="C1594" s="3" t="n">
-        <v>-139</v>
+        <v>-72</v>
       </c>
       <c r="D1594" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1594" t="inlineStr">
@@ -71216,40 +71201,40 @@
       </c>
       <c r="G1594" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1594" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1594" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" s="2" t="n">
-        <v>46353</v>
+        <v>46347</v>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Apt. SP. - Condomínio (02)</t>
         </is>
       </c>
       <c r="C1595" s="3" t="n">
-        <v>-102.5</v>
+        <v>-1063.47</v>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1595" t="inlineStr">
@@ -71259,12 +71244,17 @@
       </c>
       <c r="G1595" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1595" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1595" t="inlineStr">
@@ -71275,19 +71265,19 @@
     </row>
     <row r="1596">
       <c r="A1596" s="2" t="n">
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>TV SAMSUNG quarto do casal (7 / 8)</t>
+          <t>Aluguel de terno para Nicholas (2 / 2)</t>
         </is>
       </c>
       <c r="C1596" s="3" t="n">
-        <v>-337.49</v>
+        <v>-175</v>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1596" t="inlineStr">
@@ -71318,24 +71308,24 @@
     </row>
     <row r="1597">
       <c r="A1597" s="2" t="n">
-        <v>46357</v>
+        <v>46348</v>
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Seguro Apt Aracaju - Parcelas 4</t>
+          <t>Lata de lixo e outros utensílios domésticos</t>
         </is>
       </c>
       <c r="C1597" s="3" t="n">
-        <v>-52.85</v>
+        <v>-53.66</v>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1597" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1597" t="inlineStr">
@@ -71345,12 +71335,17 @@
       </c>
       <c r="G1597" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1597" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1597" t="inlineStr">
@@ -71361,24 +71356,24 @@
     </row>
     <row r="1598">
       <c r="A1598" s="2" t="n">
-        <v>46358</v>
+        <v>46348</v>
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>Seguro de Itens Pessoais</t>
+          <t>Casa Aracaju - Materiais para o jardim</t>
         </is>
       </c>
       <c r="C1598" s="3" t="n">
-        <v>-9.9</v>
+        <v>-112.07</v>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1598" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1598" t="inlineStr">
@@ -71388,12 +71383,17 @@
       </c>
       <c r="G1598" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1598" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1598" t="inlineStr">
@@ -71404,24 +71404,24 @@
     </row>
     <row r="1599">
       <c r="A1599" s="2" t="n">
-        <v>46362</v>
+        <v>46350</v>
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
         </is>
       </c>
       <c r="C1599" s="3" t="n">
-        <v>-17600</v>
+        <v>-500</v>
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1599" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1599" t="inlineStr">
@@ -71431,40 +71431,45 @@
       </c>
       <c r="G1599" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1599" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1599" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" s="2" t="n">
-        <v>46362</v>
+        <v>46351</v>
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>Película para RANGER XLT</t>
+          <t>Pagamento "DUO GOURMET"</t>
         </is>
       </c>
       <c r="C1600" s="3" t="n">
-        <v>-100</v>
+        <v>-45</v>
       </c>
       <c r="D1600" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1600" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1600" t="inlineStr">
@@ -71474,17 +71479,12 @@
       </c>
       <c r="G1600" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1600" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1600" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1600" t="inlineStr">
@@ -71495,19 +71495,19 @@
     </row>
     <row r="1601">
       <c r="A1601" s="2" t="n">
-        <v>46364</v>
+        <v>46353</v>
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
+          <t>Troca da bateria do MACBOOK PRO</t>
         </is>
       </c>
       <c r="C1601" s="3" t="n">
-        <v>-124.64</v>
+        <v>-102.5</v>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E1601" t="inlineStr">
@@ -71522,17 +71522,12 @@
       </c>
       <c r="G1601" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1601" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I1601" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J1601" t="inlineStr">
@@ -71543,19 +71538,19 @@
     </row>
     <row r="1602">
       <c r="A1602" s="2" t="n">
-        <v>46364</v>
+        <v>46353</v>
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
+          <t>Aquisição do celular MOTOROLA G86</t>
         </is>
       </c>
       <c r="C1602" s="3" t="n">
-        <v>-540.29</v>
+        <v>-139</v>
       </c>
       <c r="D1602" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1602" t="inlineStr">
@@ -71570,45 +71565,40 @@
       </c>
       <c r="G1602" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1602" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1602" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1602" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" s="2" t="n">
-        <v>46366</v>
+        <v>46354</v>
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Presentes comprados por Gracinha (2026.10.14)</t>
+          <t>TV SAMSUNG quarto do casal (7 / 8)</t>
         </is>
       </c>
       <c r="C1603" s="3" t="n">
-        <v>-134.38</v>
+        <v>-337.49</v>
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1603" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1603" t="inlineStr">
@@ -71634,19 +71624,19 @@
     </row>
     <row r="1604">
       <c r="A1604" s="2" t="n">
-        <v>46366</v>
+        <v>46357</v>
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>Aplicação PGBL BRASILPREV - ACMD</t>
+          <t>Seguro Apt Aracaju - Parcelas 4</t>
         </is>
       </c>
       <c r="C1604" s="3" t="n">
-        <v>-209.34</v>
+        <v>-52.85</v>
       </c>
       <c r="D1604" t="inlineStr">
         <is>
-          <t>BRASILPREV</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="E1604" t="inlineStr">
@@ -71661,35 +71651,35 @@
       </c>
       <c r="G1604" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1604" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1604" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" s="2" t="n">
-        <v>46366</v>
+        <v>46358</v>
       </c>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>Hotel Stela Maris - Salvador</t>
+          <t>Seguro de Itens Pessoais</t>
         </is>
       </c>
       <c r="C1605" s="3" t="n">
-        <v>-69.37</v>
+        <v>-9.9</v>
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Equipamentos Eletrônicos</t>
         </is>
       </c>
       <c r="E1605" t="inlineStr">
@@ -71704,17 +71694,12 @@
       </c>
       <c r="G1605" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1605" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1605" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1605" t="inlineStr">
@@ -71725,24 +71710,24 @@
     </row>
     <row r="1606">
       <c r="A1606" s="2" t="n">
-        <v>46366</v>
+        <v>46362</v>
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>Plano OSAF - Serviços Funerários</t>
+          <t>Película para RANGER XLT</t>
         </is>
       </c>
       <c r="C1606" s="3" t="n">
-        <v>-82.64</v>
+        <v>-100</v>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1606" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1606" t="inlineStr">
@@ -71752,12 +71737,17 @@
       </c>
       <c r="G1606" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1606" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1606" t="inlineStr">
@@ -71768,19 +71758,19 @@
     </row>
     <row r="1607">
       <c r="A1607" s="2" t="n">
-        <v>46366</v>
+        <v>46362</v>
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Mensalidade da hidroginástica (11 / 11)</t>
+          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
         </is>
       </c>
       <c r="C1607" s="3" t="n">
-        <v>-23.46</v>
+        <v>-17600</v>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1607" t="inlineStr">
@@ -71795,35 +71785,35 @@
       </c>
       <c r="G1607" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1607" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1607" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" s="2" t="n">
-        <v>46367</v>
+        <v>46364</v>
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
+          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
         </is>
       </c>
       <c r="C1608" s="3" t="n">
-        <v>-1818.04</v>
+        <v>-540.29</v>
       </c>
       <c r="D1608" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1608" t="inlineStr">
@@ -71838,35 +71828,40 @@
       </c>
       <c r="G1608" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1608" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1608" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1608" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" s="2" t="n">
-        <v>46369</v>
+        <v>46364</v>
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
+          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
         </is>
       </c>
       <c r="C1609" s="3" t="n">
-        <v>-93.89</v>
+        <v>-124.64</v>
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1609" t="inlineStr">
@@ -71881,17 +71876,17 @@
       </c>
       <c r="G1609" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1609" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1609" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1609" t="inlineStr">
@@ -71902,24 +71897,24 @@
     </row>
     <row r="1610">
       <c r="A1610" s="2" t="n">
-        <v>46369</v>
+        <v>46366</v>
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
+          <t>Presentes comprados por Gracinha (2026.10.14)</t>
         </is>
       </c>
       <c r="C1610" s="3" t="n">
-        <v>-58.07</v>
+        <v>-134.38</v>
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1610" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1610" t="inlineStr">
@@ -71929,40 +71924,40 @@
       </c>
       <c r="G1610" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1610" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1610" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" s="2" t="n">
-        <v>46369</v>
+        <v>46366</v>
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>Seguro da Hilux SW4</t>
+          <t>Aplicação PGBL BRASILPREV - ACMD</t>
         </is>
       </c>
       <c r="C1611" s="3" t="n">
-        <v>-233.11</v>
+        <v>-209.34</v>
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>BRASILPREV</t>
         </is>
       </c>
       <c r="E1611" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1611" t="inlineStr">
@@ -71972,45 +71967,40 @@
       </c>
       <c r="G1611" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1611" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1611" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1611" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" s="2" t="n">
-        <v>46371</v>
+        <v>46366</v>
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Pagamento Clube SMILES</t>
+          <t>Hotel Stela Maris - Salvador</t>
         </is>
       </c>
       <c r="C1612" s="3" t="n">
-        <v>-46</v>
+        <v>-69.37</v>
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1612" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1612" t="inlineStr">
@@ -72041,24 +72031,24 @@
     </row>
     <row r="1613">
       <c r="A1613" s="2" t="n">
-        <v>46371</v>
+        <v>46366</v>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Plano OSAF - Serviços Funerários</t>
         </is>
       </c>
       <c r="C1613" s="3" t="n">
-        <v>-52.83</v>
+        <v>-82.64</v>
       </c>
       <c r="D1613" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1613" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1613" t="inlineStr">
@@ -72068,12 +72058,12 @@
       </c>
       <c r="G1613" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1613" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1613" t="inlineStr">
@@ -72084,24 +72074,24 @@
     </row>
     <row r="1614">
       <c r="A1614" s="2" t="n">
-        <v>46372</v>
+        <v>46366</v>
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>Transporte Terrestre, Hoteis e Excursão</t>
+          <t>Mensalidade da hidroginástica (11 / 11)</t>
         </is>
       </c>
       <c r="C1614" s="3" t="n">
-        <v>-1824.26</v>
+        <v>-23.46</v>
       </c>
       <c r="D1614" t="inlineStr">
         <is>
-          <t>VIAGENS/Passeios</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1614" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1614" t="inlineStr">
@@ -72111,17 +72101,12 @@
       </c>
       <c r="G1614" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1614" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1614" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1614" t="inlineStr">
@@ -72132,19 +72117,19 @@
     </row>
     <row r="1615">
       <c r="A1615" s="2" t="n">
-        <v>46375</v>
+        <v>46367</v>
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
         </is>
       </c>
       <c r="C1615" s="3" t="n">
-        <v>-8.99</v>
+        <v>-1818.04</v>
       </c>
       <c r="D1615" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1615" t="inlineStr">
@@ -72159,35 +72144,35 @@
       </c>
       <c r="G1615" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1615" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1615" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" s="2" t="n">
-        <v>46378</v>
+        <v>46369</v>
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
         </is>
       </c>
       <c r="C1616" s="3" t="n">
-        <v>-112.07</v>
+        <v>-93.89</v>
       </c>
       <c r="D1616" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1616" t="inlineStr">
@@ -72202,17 +72187,17 @@
       </c>
       <c r="G1616" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="H1616" t="inlineStr">
         <is>
-          <t>Manutenção e encargos</t>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1616" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1616" t="inlineStr">
@@ -72223,19 +72208,19 @@
     </row>
     <row r="1617">
       <c r="A1617" s="2" t="n">
-        <v>46378</v>
+        <v>46369</v>
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
         </is>
       </c>
       <c r="C1617" s="3" t="n">
-        <v>-53.66</v>
+        <v>-58.07</v>
       </c>
       <c r="D1617" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1617" t="inlineStr">
@@ -72250,40 +72235,35 @@
       </c>
       <c r="G1617" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1617" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1617" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1617" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" s="2" t="n">
-        <v>46380</v>
+        <v>46369</v>
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Seguro da Hilux SW4</t>
         </is>
       </c>
       <c r="C1618" s="3" t="n">
-        <v>-500</v>
+        <v>-233.11</v>
       </c>
       <c r="D1618" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1618" t="inlineStr">
@@ -72308,7 +72288,7 @@
       </c>
       <c r="I1618" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1618" t="inlineStr">
@@ -72319,19 +72299,19 @@
     </row>
     <row r="1619">
       <c r="A1619" s="2" t="n">
-        <v>46383</v>
+        <v>46371</v>
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1619" s="3" t="n">
-        <v>-139</v>
+        <v>-52.83</v>
       </c>
       <c r="D1619" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1619" t="inlineStr">
@@ -72346,35 +72326,35 @@
       </c>
       <c r="G1619" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1619" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1619" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" s="2" t="n">
-        <v>46383</v>
+        <v>46371</v>
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Pagamento Clube SMILES</t>
         </is>
       </c>
       <c r="C1620" s="3" t="n">
-        <v>-102.5</v>
+        <v>-46</v>
       </c>
       <c r="D1620" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1620" t="inlineStr">
@@ -72389,12 +72369,17 @@
       </c>
       <c r="G1620" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1620" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1620" t="inlineStr">
@@ -72405,49 +72390,370 @@
     </row>
     <row r="1621">
       <c r="A1621" s="2" t="n">
+        <v>46372</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Transporte Terrestre, Hoteis e Excursão</t>
+        </is>
+      </c>
+      <c r="C1621" s="3" t="n">
+        <v>-1824.26</v>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>VIAGENS/Passeios</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1621" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
+        </is>
+      </c>
+      <c r="I1621" t="inlineStr">
+        <is>
+          <t>Despesas com lazer</t>
+        </is>
+      </c>
+      <c r="J1621" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="2" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Perfume no Boticário</t>
+        </is>
+      </c>
+      <c r="C1622" s="3" t="n">
+        <v>-8.99</v>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>Salão de Beleza e Cosméticos</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>FAMÍLIA</t>
+        </is>
+      </c>
+      <c r="I1622" t="inlineStr">
+        <is>
+          <t>Despesas com família</t>
+        </is>
+      </c>
+      <c r="J1622" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="2" t="n">
+        <v>46378</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Lata de lixo e outros utensílios domésticos</t>
+        </is>
+      </c>
+      <c r="C1623" s="3" t="n">
+        <v>-53.66</v>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>Restauração e Manutenção</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1623" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
+        </is>
+      </c>
+      <c r="I1623" t="inlineStr">
+        <is>
+          <t>Despesas com imóveis</t>
+        </is>
+      </c>
+      <c r="J1623" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="2" t="n">
+        <v>46378</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Casa Aracaju - Materiais para o jardim</t>
+        </is>
+      </c>
+      <c r="C1624" s="3" t="n">
+        <v>-112.07</v>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>Restauração e Manutenção</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
+        </is>
+      </c>
+      <c r="I1624" t="inlineStr">
+        <is>
+          <t>Despesas com imóveis</t>
+        </is>
+      </c>
+      <c r="J1624" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="2" t="n">
+        <v>46380</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+        </is>
+      </c>
+      <c r="C1625" s="3" t="n">
+        <v>-500</v>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>Automóvel/Manutenção</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
+        </is>
+      </c>
+      <c r="I1625" t="inlineStr">
+        <is>
+          <t>Despesas com Automóvel (Manutenção)</t>
+        </is>
+      </c>
+      <c r="J1625" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="2" t="n">
+        <v>46383</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Troca da bateria do MACBOOK PRO</t>
+        </is>
+      </c>
+      <c r="C1626" s="3" t="n">
+        <v>-102.5</v>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>OUTRAS DESPESAS</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>OUTRAS DESPESAS</t>
+        </is>
+      </c>
+      <c r="I1626" t="inlineStr">
+        <is>
+          <t>Outras Despesas</t>
+        </is>
+      </c>
+      <c r="J1626" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="2" t="n">
+        <v>46383</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Aquisição do celular MOTOROLA G86</t>
+        </is>
+      </c>
+      <c r="C1627" s="3" t="n">
+        <v>-139</v>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>Eletrônicos</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>BENS DURÁVEIS</t>
+        </is>
+      </c>
+      <c r="I1627" t="inlineStr">
+        <is>
+          <t>Investimentos Bens</t>
+        </is>
+      </c>
+      <c r="J1627" t="inlineStr">
+        <is>
+          <t>Investimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="2" t="n">
         <v>46384</v>
       </c>
-      <c r="B1621" t="inlineStr">
+      <c r="B1628" t="inlineStr">
         <is>
           <t>TV SAMSUNG quarto do casal (8 / 8)</t>
         </is>
       </c>
-      <c r="C1621" s="3" t="n">
+      <c r="C1628" s="3" t="n">
         <v>-337.48</v>
       </c>
-      <c r="D1621" t="inlineStr">
+      <c r="D1628" t="inlineStr">
         <is>
           <t>Acessórios</t>
         </is>
       </c>
-      <c r="E1621" t="inlineStr">
-        <is>
-          <t>Cartão BB VISA</t>
-        </is>
-      </c>
-      <c r="F1621" t="inlineStr">
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="G1621" t="inlineStr">
+      <c r="G1628" t="inlineStr">
         <is>
           <t>FAMÍLIA</t>
         </is>
       </c>
-      <c r="I1621" t="inlineStr">
+      <c r="I1628" t="inlineStr">
         <is>
           <t>Despesas com família</t>
         </is>
       </c>
-      <c r="J1621" t="inlineStr">
+      <c r="J1628" t="inlineStr">
         <is>
           <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1621"/>
+  <autoFilter ref="A1:J1628"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Arquivos_Origem/Registros_2026.xlsx
+++ b/Arquivos_Origem/Registros_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Transações" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transações" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transações'!$A$1:$J$1630</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transações'!$A$1:$J$1632</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1630"/>
+  <dimension ref="A1:J1632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,20 +540,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Combustível para a HILUX</t>
+          <t>Ajuda aos necessitados</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>-230.4</v>
+        <v>-60</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Combustível</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Despesas com Combustível</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,20 +583,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alimentos e Materiais de limpeza</t>
+          <t>Serviço Apartamento 42 - São Paulo (P 2)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-924.88</v>
+        <v>-2801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -626,20 +626,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apt. Aju. - Energia Elétrica</t>
+          <t>Alimentos e Materiais de limpeza</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-214.23</v>
+        <v>-924.88</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -649,17 +649,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -674,15 +669,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ajuda aos necessitados</t>
+          <t>Apt. Aju. - Energia Elétrica</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-60</v>
+        <v>-214.23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -697,12 +692,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -717,20 +717,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Serviço Apartamento 42 - São Paulo (P 2)</t>
+          <t>Combustível para a HILUX</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-2801</v>
+        <v>-230.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Combustível</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com Combustível</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -851,15 +851,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Café da manhã com Gracinha</t>
+          <t>Alimentos e Materiais de limpeza</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-98.5</v>
+        <v>-97.89</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -894,20 +894,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alimentos e Materiais de limpeza</t>
+          <t>Ajuda a Casa do Pobre</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-97.89</v>
+        <v>-30</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -937,15 +937,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ajuda a Casa do Pobre</t>
+          <t>Hotel Real Classic para IPD</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-30</v>
+        <v>-94.56</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -960,12 +960,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -980,15 +985,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ovos</t>
+          <t>Café da manhã com Gracinha</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-15.5</v>
+        <v>-98.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1023,20 +1028,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hotel Real Classic para IPD</t>
+          <t>Ovos</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-94.56</v>
+        <v>-15.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Padaria</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1046,17 +1051,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -36283,11 +36283,11 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Casa Aracaju -  Peças para o conserto bomba do jardim</t>
+          <t>Casa Aracaju - Conserto da Bomba do jardim</t>
         </is>
       </c>
       <c r="C809" s="3" t="n">
-        <v>-26.5</v>
+        <v>-250</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F809" t="inlineStr">
@@ -36675,11 +36675,11 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Conserto da Bomba do jardim</t>
+          <t>Casa Aracaju -  Peças para o conserto bomba do jardim</t>
         </is>
       </c>
       <c r="C818" s="3" t="n">
-        <v>-250</v>
+        <v>-26.5</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
@@ -36938,20 +36938,20 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Ajuda a Casa do Pobre</t>
+          <t>Café da manhã</t>
         </is>
       </c>
       <c r="C824" s="3" t="n">
-        <v>-30</v>
+        <v>-38.83</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
@@ -36961,12 +36961,12 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
@@ -37029,20 +37029,20 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Café da manhã</t>
+          <t>Ajuda a Casa do Pobre</t>
         </is>
       </c>
       <c r="C826" s="3" t="n">
-        <v>-38.83</v>
+        <v>-30</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -37052,12 +37052,12 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
@@ -54809,20 +54809,20 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Alimentos e Materiais de limpeza (10 / 10)</t>
+          <t>Perfume no Boticário (2 / 10)</t>
         </is>
       </c>
       <c r="C1226" s="3" t="n">
-        <v>-24.8</v>
+        <v>-8.99</v>
       </c>
       <c r="D1226" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1226" t="inlineStr">
         <is>
-          <t>Cartão BB ELO</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1226" t="inlineStr">
@@ -54832,12 +54832,12 @@
       </c>
       <c r="G1226" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1226" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1226" t="inlineStr">
@@ -54852,20 +54852,20 @@
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Perfume no Boticário (2 / 10)</t>
+          <t>Alimentos e Materiais de limpeza (10 / 10)</t>
         </is>
       </c>
       <c r="C1227" s="3" t="n">
-        <v>-8.99</v>
+        <v>-24.8</v>
       </c>
       <c r="D1227" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1227" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Cartão BB ELO</t>
         </is>
       </c>
       <c r="F1227" t="inlineStr">
@@ -54875,12 +54875,12 @@
       </c>
       <c r="G1227" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1227" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1227" t="inlineStr">
@@ -63861,20 +63861,20 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Energia Elétrica</t>
+          <t>Rendimentos Saldo Conta WISE</t>
         </is>
       </c>
       <c r="C1430" s="3" t="n">
-        <v>-213.57</v>
+        <v>37.28</v>
       </c>
       <c r="D1430" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Juros de Investimento</t>
         </is>
       </c>
       <c r="E1430" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão WISE</t>
         </is>
       </c>
       <c r="F1430" t="inlineStr">
@@ -63884,22 +63884,22 @@
       </c>
       <c r="G1430" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>RECEITAS</t>
         </is>
       </c>
       <c r="H1430" t="inlineStr">
         <is>
-          <t>Contas da casa</t>
+          <t>Financeiras</t>
         </is>
       </c>
       <c r="I1430" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1430" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -64086,20 +64086,20 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Rendimentos Saldo Conta WISE</t>
+          <t>Casa Aracaju - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1435" s="3" t="n">
-        <v>37.28</v>
+        <v>-213.57</v>
       </c>
       <c r="D1435" t="inlineStr">
         <is>
-          <t>Juros de Investimento</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1435" t="inlineStr">
         <is>
-          <t>Cartão WISE</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1435" t="inlineStr">
@@ -64109,22 +64109,22 @@
       </c>
       <c r="G1435" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1435" t="inlineStr">
         <is>
-          <t>Financeiras</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1435" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1435" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -64230,15 +64230,15 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Garafas de água</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1438" s="3" t="n">
-        <v>-14</v>
+        <v>-93.98999999999999</v>
       </c>
       <c r="D1438" t="inlineStr">
         <is>
-          <t>VIAGENS/Alimentação</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1438" t="inlineStr">
@@ -64253,17 +64253,12 @@
       </c>
       <c r="G1438" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1438" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1438" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1438" t="inlineStr">
@@ -64278,15 +64273,15 @@
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Garafas de água</t>
         </is>
       </c>
       <c r="C1439" s="3" t="n">
-        <v>-93.98999999999999</v>
+        <v>-14</v>
       </c>
       <c r="D1439" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>VIAGENS/Alimentação</t>
         </is>
       </c>
       <c r="E1439" t="inlineStr">
@@ -64301,12 +64296,17 @@
       </c>
       <c r="G1439" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1439" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1439" t="inlineStr">
@@ -68928,11 +68928,11 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>Benefício PETROS II</t>
+          <t>Benefício PETROS</t>
         </is>
       </c>
       <c r="C1544" s="3" t="n">
-        <v>4694.46</v>
+        <v>10524.94</v>
       </c>
       <c r="D1544" t="inlineStr">
         <is>
@@ -69024,11 +69024,11 @@
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>Benefício PETROS</t>
+          <t>Benefício PETROS II</t>
         </is>
       </c>
       <c r="C1546" s="3" t="n">
-        <v>10524.94</v>
+        <v>4694.46</v>
       </c>
       <c r="D1546" t="inlineStr">
         <is>
@@ -69163,15 +69163,15 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>Passagem GRU / AJU - ACMD e MGAP - 21/11/2026 (2 / 2)</t>
+          <t>Link de Internet - CLARO</t>
         </is>
       </c>
       <c r="C1549" s="3" t="n">
-        <v>-312</v>
+        <v>-267.06</v>
       </c>
       <c r="D1549" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="E1549" t="inlineStr">
@@ -69186,17 +69186,12 @@
       </c>
       <c r="G1549" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1549" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1549" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1549" t="inlineStr">
@@ -69211,20 +69206,20 @@
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Salada de frutas</t>
+          <t>Pagamento "DUO GOURMET"</t>
         </is>
       </c>
       <c r="C1550" s="3" t="n">
-        <v>-29.15</v>
+        <v>-45</v>
       </c>
       <c r="D1550" t="inlineStr">
         <is>
-          <t>Lanchonete</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1550" t="inlineStr">
@@ -69254,15 +69249,15 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Link de Internet - CLARO</t>
+          <t>Passagem GRU / AJU - ACMD e MGAP - 21/11/2026 (2 / 2)</t>
         </is>
       </c>
       <c r="C1551" s="3" t="n">
-        <v>-267.06</v>
+        <v>-312</v>
       </c>
       <c r="D1551" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1551" t="inlineStr">
@@ -69277,12 +69272,17 @@
       </c>
       <c r="G1551" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1551" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1551" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1551" t="inlineStr">
@@ -69297,20 +69297,20 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Pagamento "DUO GOURMET"</t>
+          <t>Salada de frutas</t>
         </is>
       </c>
       <c r="C1552" s="3" t="n">
-        <v>-45</v>
+        <v>-29.15</v>
       </c>
       <c r="D1552" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Lanchonete</t>
         </is>
       </c>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1552" t="inlineStr">
@@ -69340,20 +69340,20 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>Combustível para RANGER XLT</t>
+          <t>Apt.AJU. - Investimento Cozinha</t>
         </is>
       </c>
       <c r="C1553" s="3" t="n">
-        <v>-364.5</v>
+        <v>-1500</v>
       </c>
       <c r="D1553" t="inlineStr">
         <is>
-          <t>Combustível</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1553" t="inlineStr">
@@ -69363,17 +69363,17 @@
       </c>
       <c r="G1553" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1553" t="inlineStr">
         <is>
-          <t>Despesas com Combustível</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1553" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
@@ -69383,15 +69383,15 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Combustível para RANGER XLT</t>
         </is>
       </c>
       <c r="C1554" s="3" t="n">
-        <v>-102.5</v>
+        <v>-364.5</v>
       </c>
       <c r="D1554" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Combustível</t>
         </is>
       </c>
       <c r="E1554" t="inlineStr">
@@ -69406,12 +69406,12 @@
       </c>
       <c r="G1554" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I1554" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com Combustível</t>
         </is>
       </c>
       <c r="J1554" t="inlineStr">
@@ -69426,15 +69426,15 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Troca da bateria do MACBOOK PRO</t>
         </is>
       </c>
       <c r="C1555" s="3" t="n">
-        <v>-139</v>
+        <v>-102.5</v>
       </c>
       <c r="D1555" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E1555" t="inlineStr">
@@ -69449,17 +69449,17 @@
       </c>
       <c r="G1555" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I1555" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J1555" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -69469,20 +69469,20 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Apt.AJU. - Investimento Cozinha</t>
+          <t>Aquisição do celular MOTOROLA G86</t>
         </is>
       </c>
       <c r="C1556" s="3" t="n">
-        <v>-1500</v>
+        <v>-139</v>
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1556" t="inlineStr">
@@ -69497,12 +69497,12 @@
       </c>
       <c r="I1556" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1556" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
@@ -69512,20 +69512,20 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>TV SAMSUNG quarto do casal (6 / 8)</t>
+          <t>Apt. SP. - Gás Natural</t>
         </is>
       </c>
       <c r="C1557" s="3" t="n">
-        <v>-337.49</v>
+        <v>-63.96</v>
       </c>
       <c r="D1557" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Gás</t>
         </is>
       </c>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -69535,12 +69535,17 @@
       </c>
       <c r="G1557" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1557" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1557" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1557" t="inlineStr">
@@ -69598,35 +69603,35 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Estacionamento</t>
+          <t>TV SAMSUNG quarto do casal (6 / 8)</t>
         </is>
       </c>
       <c r="C1559" s="3" t="n">
-        <v>-5</v>
+        <v>-337.49</v>
       </c>
       <c r="D1559" t="inlineStr">
         <is>
-          <t>Estacionamento</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1559" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1559" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1559" t="inlineStr">
         <is>
-          <t>Despesas com Estacionamento</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1559" t="inlineStr">
@@ -69641,15 +69646,15 @@
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Apt. SP. - Gás Natural</t>
+          <t>Estacionamento</t>
         </is>
       </c>
       <c r="C1560" s="3" t="n">
-        <v>-63.96</v>
+        <v>-5</v>
       </c>
       <c r="D1560" t="inlineStr">
         <is>
-          <t>Gás</t>
+          <t>Estacionamento</t>
         </is>
       </c>
       <c r="E1560" t="inlineStr">
@@ -69659,22 +69664,17 @@
       </c>
       <c r="F1560" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1560" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1560" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I1560" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Estacionamento</t>
         </is>
       </c>
       <c r="J1560" t="inlineStr">
@@ -69728,24 +69728,24 @@
     </row>
     <row r="1562">
       <c r="A1562" s="2" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Água e Esgoto</t>
+          <t>Alimentos</t>
         </is>
       </c>
       <c r="C1562" s="3" t="n">
-        <v>-108.5</v>
+        <v>-205.07</v>
       </c>
       <c r="D1562" t="inlineStr">
         <is>
-          <t>Água e Esgoto</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1562" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1562" t="inlineStr">
@@ -69755,17 +69755,12 @@
       </c>
       <c r="G1562" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1562" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1562" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1562" t="inlineStr">
@@ -69776,24 +69771,24 @@
     </row>
     <row r="1563">
       <c r="A1563" s="2" t="n">
-        <v>46327</v>
+        <v>46324</v>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Seguro Apt Aracaju - Parcelas 3</t>
+          <t>Almoço com Gracinha</t>
         </is>
       </c>
       <c r="C1563" s="3" t="n">
-        <v>-52.85</v>
+        <v>-228.5</v>
       </c>
       <c r="D1563" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1563" t="inlineStr">
@@ -69803,12 +69798,12 @@
       </c>
       <c r="G1563" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1563" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1563" t="inlineStr">
@@ -69819,19 +69814,19 @@
     </row>
     <row r="1564">
       <c r="A1564" s="2" t="n">
-        <v>46327</v>
+        <v>46325</v>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>Cemitério Colina da Saudade 2026</t>
+          <t>Casa Aracaju - Água e Esgoto</t>
         </is>
       </c>
       <c r="C1564" s="3" t="n">
-        <v>-600</v>
+        <v>-108.5</v>
       </c>
       <c r="D1564" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>Água e Esgoto</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
@@ -69846,12 +69841,17 @@
       </c>
       <c r="G1564" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1564" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1564" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1564" t="inlineStr">
@@ -69862,19 +69862,19 @@
     </row>
     <row r="1565">
       <c r="A1565" s="2" t="n">
-        <v>46328</v>
+        <v>46327</v>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>Seguro de Itens Pessoais</t>
+          <t>Cemitério Colina da Saudade 2026</t>
         </is>
       </c>
       <c r="C1565" s="3" t="n">
-        <v>-9.9</v>
+        <v>-600</v>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1565" t="inlineStr">
@@ -69905,19 +69905,19 @@
     </row>
     <row r="1566">
       <c r="A1566" s="2" t="n">
-        <v>46329</v>
+        <v>46327</v>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Energia Elétrica</t>
+          <t>Seguro Apt Aracaju - Parcelas 3</t>
         </is>
       </c>
       <c r="C1566" s="3" t="n">
-        <v>-182</v>
+        <v>-52.85</v>
       </c>
       <c r="D1566" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="E1566" t="inlineStr">
@@ -69932,17 +69932,12 @@
       </c>
       <c r="G1566" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1566" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1566" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1566" t="inlineStr">
@@ -69953,19 +69948,19 @@
     </row>
     <row r="1567">
       <c r="A1567" s="2" t="n">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>Apt. Aju. - Energia Elétrica</t>
+          <t>Seguro de Itens Pessoais</t>
         </is>
       </c>
       <c r="C1567" s="3" t="n">
-        <v>-169.78</v>
+        <v>-9.9</v>
       </c>
       <c r="D1567" t="inlineStr">
         <is>
-          <t>Energia Elétrica</t>
+          <t>Equipamentos Eletrônicos</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
@@ -69980,17 +69975,12 @@
       </c>
       <c r="G1567" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1567" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1567" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1567" t="inlineStr">
@@ -70005,15 +69995,15 @@
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
+          <t>Casa Aracaju - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1568" s="3" t="n">
-        <v>200000</v>
+        <v>-182</v>
       </c>
       <c r="D1568" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1568" t="inlineStr">
@@ -70028,35 +70018,40 @@
       </c>
       <c r="G1568" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1568" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1568" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1568" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" s="2" t="n">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
+          <t>Apt. Aju. - Energia Elétrica</t>
         </is>
       </c>
       <c r="C1569" s="3" t="n">
-        <v>-17600</v>
+        <v>-169.78</v>
       </c>
       <c r="D1569" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Energia Elétrica</t>
         </is>
       </c>
       <c r="E1569" t="inlineStr">
@@ -70071,40 +70066,45 @@
       </c>
       <c r="G1569" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1569" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1569" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" s="2" t="n">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>Película para RANGER XLT</t>
+          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
         </is>
       </c>
       <c r="C1570" s="3" t="n">
-        <v>-100</v>
+        <v>200000</v>
       </c>
       <c r="D1570" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1570" t="inlineStr">
@@ -70114,22 +70114,17 @@
       </c>
       <c r="G1570" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1570" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1570" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1570" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -70139,20 +70134,20 @@
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Filtro para a COIFA - CONSUL</t>
+          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
         </is>
       </c>
       <c r="C1571" s="3" t="n">
-        <v>-138.27</v>
+        <v>-17600</v>
       </c>
       <c r="D1571" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>Cartão BB ELO</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1571" t="inlineStr">
@@ -70162,45 +70157,40 @@
       </c>
       <c r="G1571" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1571" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1571" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1571" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" s="2" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (01)</t>
+          <t>Película para RANGER XLT</t>
         </is>
       </c>
       <c r="C1572" s="3" t="n">
-        <v>-1429.33</v>
+        <v>-100</v>
       </c>
       <c r="D1572" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1572" t="inlineStr">
@@ -70210,17 +70200,17 @@
       </c>
       <c r="G1572" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="H1572" t="inlineStr">
         <is>
-          <t>Contas da casa</t>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1572" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1572" t="inlineStr">
@@ -70231,24 +70221,24 @@
     </row>
     <row r="1573">
       <c r="A1573" s="2" t="n">
-        <v>46334</v>
+        <v>46332</v>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>Sapato para ACMD</t>
+          <t>Filtro para a COIFA - CONSUL</t>
         </is>
       </c>
       <c r="C1573" s="3" t="n">
-        <v>-121.6</v>
+        <v>-138.27</v>
       </c>
       <c r="D1573" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Cartão BB ELO</t>
         </is>
       </c>
       <c r="F1573" t="inlineStr">
@@ -70258,12 +70248,17 @@
       </c>
       <c r="G1573" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1573" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1573" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1573" t="inlineStr">
@@ -70274,24 +70269,24 @@
     </row>
     <row r="1574">
       <c r="A1574" s="2" t="n">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
+          <t>Apt. SP. - Condomínio (01)</t>
         </is>
       </c>
       <c r="C1574" s="3" t="n">
-        <v>-540.29</v>
+        <v>-1429.33</v>
       </c>
       <c r="D1574" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1574" t="inlineStr">
@@ -70301,17 +70296,17 @@
       </c>
       <c r="G1574" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1574" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1574" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1574" t="inlineStr">
@@ -70326,15 +70321,15 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
+          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
         </is>
       </c>
       <c r="C1575" s="3" t="n">
-        <v>-124.64</v>
+        <v>-540.29</v>
       </c>
       <c r="D1575" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1575" t="inlineStr">
@@ -70370,24 +70365,24 @@
     </row>
     <row r="1576">
       <c r="A1576" s="2" t="n">
-        <v>46335</v>
+        <v>46334</v>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
+          <t>Sapato para ACMD</t>
         </is>
       </c>
       <c r="C1576" s="3" t="n">
-        <v>300000</v>
+        <v>-121.6</v>
       </c>
       <c r="D1576" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1576" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1576" t="inlineStr">
@@ -70397,40 +70392,40 @@
       </c>
       <c r="G1576" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1576" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1576" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" s="2" t="n">
-        <v>46336</v>
+        <v>46334</v>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
         </is>
       </c>
       <c r="C1577" s="3" t="n">
-        <v>-300000</v>
+        <v>-124.64</v>
       </c>
       <c r="D1577" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1577" t="inlineStr">
@@ -70440,35 +70435,40 @@
       </c>
       <c r="G1577" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1577" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1577" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" s="2" t="n">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Mensalidade da hidroginástica (10 / 11)</t>
+          <t>Resgate Parcial BB Deb Inc CDI Pvt</t>
         </is>
       </c>
       <c r="C1578" s="3" t="n">
-        <v>-88</v>
+        <v>300000</v>
       </c>
       <c r="D1578" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1578" t="inlineStr">
@@ -70483,17 +70483,17 @@
       </c>
       <c r="G1578" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1578" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1578" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -70503,15 +70503,15 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Plano OSAF - Serviços Funerários</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1579" s="3" t="n">
-        <v>-82.64</v>
+        <v>-300000</v>
       </c>
       <c r="D1579" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1579" t="inlineStr">
@@ -70526,17 +70526,17 @@
       </c>
       <c r="G1579" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1579" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1579" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -70546,15 +70546,15 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>Hotel Stela Maris - Salvador</t>
+          <t>Mensalidade da hidroginástica (10 / 11)</t>
         </is>
       </c>
       <c r="C1580" s="3" t="n">
-        <v>-69.37</v>
+        <v>-88</v>
       </c>
       <c r="D1580" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1580" t="inlineStr">
@@ -70569,17 +70569,12 @@
       </c>
       <c r="G1580" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1580" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1580" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1580" t="inlineStr">
@@ -70594,15 +70589,15 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Aplicação PGBL BRASILPREV - ACMD</t>
+          <t>Plano OSAF - Serviços Funerários</t>
         </is>
       </c>
       <c r="C1581" s="3" t="n">
-        <v>-209.34</v>
+        <v>-82.64</v>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
-          <t>BRASILPREV</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1581" t="inlineStr">
@@ -70617,17 +70612,17 @@
       </c>
       <c r="G1581" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1581" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1581" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -70637,15 +70632,15 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>Presentes comprados por Gracinha (2026.10.14)</t>
+          <t>Hotel Stela Maris - Salvador</t>
         </is>
       </c>
       <c r="C1582" s="3" t="n">
-        <v>-134.38</v>
+        <v>-69.37</v>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1582" t="inlineStr">
@@ -70660,12 +70655,17 @@
       </c>
       <c r="G1582" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1582" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1582" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1582" t="inlineStr">
@@ -70680,15 +70680,15 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Condomínio</t>
+          <t>Aplicação PGBL BRASILPREV - ACMD</t>
         </is>
       </c>
       <c r="C1583" s="3" t="n">
-        <v>-1650</v>
+        <v>-209.34</v>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>BRASILPREV</t>
         </is>
       </c>
       <c r="E1583" t="inlineStr">
@@ -70703,22 +70703,17 @@
       </c>
       <c r="G1583" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1583" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1583" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1583" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -70728,15 +70723,15 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Taxa Extra (9 de 12 )</t>
+          <t>Presentes comprados por Gracinha (2026.10.14)</t>
         </is>
       </c>
       <c r="C1584" s="3" t="n">
-        <v>-500</v>
+        <v>-134.38</v>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1584" t="inlineStr">
@@ -70751,40 +70746,40 @@
       </c>
       <c r="G1584" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1584" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1584" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" s="2" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
+          <t>Casa Aracaju - Condomínio</t>
         </is>
       </c>
       <c r="C1585" s="3" t="n">
-        <v>-1818.04</v>
+        <v>-1650</v>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1585" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1585" t="inlineStr">
@@ -70794,40 +70789,45 @@
       </c>
       <c r="G1585" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1585" t="inlineStr">
+        <is>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1585" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1585" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" s="2" t="n">
-        <v>46338</v>
+        <v>46336</v>
       </c>
       <c r="B1586" t="inlineStr">
         <is>
-          <t>Aluguel do terno para o casamento de João Paulo</t>
+          <t>Casa Aracaju - Taxa Extra (9 de 12 )</t>
         </is>
       </c>
       <c r="C1586" s="3" t="n">
-        <v>-116.67</v>
+        <v>-500</v>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1586" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1586" t="inlineStr">
@@ -70837,35 +70837,35 @@
       </c>
       <c r="G1586" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1586" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1586" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" s="2" t="n">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
+          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
         </is>
       </c>
       <c r="C1587" s="3" t="n">
-        <v>-58.07</v>
+        <v>-1818.04</v>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1587" t="inlineStr">
@@ -70885,30 +70885,30 @@
       </c>
       <c r="I1587" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1587" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" s="2" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Seguro da Hilux SW4</t>
+          <t>Aluguel do terno para o casamento de João Paulo</t>
         </is>
       </c>
       <c r="C1588" s="3" t="n">
-        <v>-233.11</v>
+        <v>-116.67</v>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1588" t="inlineStr">
@@ -70923,17 +70923,12 @@
       </c>
       <c r="G1588" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1588" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1588" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1588" t="inlineStr">
@@ -70992,19 +70987,19 @@
     </row>
     <row r="1590">
       <c r="A1590" s="2" t="n">
-        <v>46341</v>
+        <v>46339</v>
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Seguro da Hilux SW4</t>
         </is>
       </c>
       <c r="C1590" s="3" t="n">
-        <v>-52.83</v>
+        <v>-233.11</v>
       </c>
       <c r="D1590" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1590" t="inlineStr">
@@ -71019,12 +71014,17 @@
       </c>
       <c r="G1590" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1590" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1590" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1590" t="inlineStr">
@@ -71035,19 +71035,19 @@
     </row>
     <row r="1591">
       <c r="A1591" s="2" t="n">
-        <v>46341</v>
+        <v>46339</v>
       </c>
       <c r="B1591" t="inlineStr">
         <is>
-          <t>Pagamento Clube SMILES</t>
+          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
         </is>
       </c>
       <c r="C1591" s="3" t="n">
-        <v>-46</v>
+        <v>-58.07</v>
       </c>
       <c r="D1591" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1591" t="inlineStr">
@@ -71062,40 +71062,35 @@
       </c>
       <c r="G1591" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1591" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1591" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1591" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" s="2" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="B1592" t="inlineStr">
         <is>
-          <t>Transporte Terrestre, Hoteis e Excursão</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1592" s="3" t="n">
-        <v>-1824.26</v>
+        <v>-52.83</v>
       </c>
       <c r="D1592" t="inlineStr">
         <is>
-          <t>VIAGENS/Passeios</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1592" t="inlineStr">
@@ -71110,17 +71105,12 @@
       </c>
       <c r="G1592" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1592" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1592" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1592" t="inlineStr">
@@ -71131,19 +71121,19 @@
     </row>
     <row r="1593">
       <c r="A1593" s="2" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>Academia ACMD</t>
+          <t>Pagamento Clube SMILES</t>
         </is>
       </c>
       <c r="C1593" s="3" t="n">
-        <v>-448.35</v>
+        <v>-46</v>
       </c>
       <c r="D1593" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1593" t="inlineStr">
@@ -71158,12 +71148,17 @@
       </c>
       <c r="G1593" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1593" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1593" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1593" t="inlineStr">
@@ -71174,19 +71169,19 @@
     </row>
     <row r="1594">
       <c r="A1594" s="2" t="n">
-        <v>46345</v>
+        <v>46342</v>
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Academia ACMD</t>
         </is>
       </c>
       <c r="C1594" s="3" t="n">
-        <v>-8.99</v>
+        <v>-448.35</v>
       </c>
       <c r="D1594" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1594" t="inlineStr">
@@ -71217,19 +71212,19 @@
     </row>
     <row r="1595">
       <c r="A1595" s="2" t="n">
-        <v>46346</v>
+        <v>46342</v>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Sacos para os alimentos dos necessitados (2 / 2)</t>
+          <t>Transporte Terrestre, Hoteis e Excursão</t>
         </is>
       </c>
       <c r="C1595" s="3" t="n">
-        <v>-72</v>
+        <v>-1824.26</v>
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>VIAGENS/Passeios</t>
         </is>
       </c>
       <c r="E1595" t="inlineStr">
@@ -71244,12 +71239,17 @@
       </c>
       <c r="G1595" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1595" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1595" t="inlineStr">
@@ -71260,19 +71260,19 @@
     </row>
     <row r="1596">
       <c r="A1596" s="2" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>Materiais de limpeza (2 / 2)</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1596" s="3" t="n">
-        <v>-110.2</v>
+        <v>-8.99</v>
       </c>
       <c r="D1596" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1596" t="inlineStr">
@@ -71287,12 +71287,12 @@
       </c>
       <c r="G1596" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1596" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1596" t="inlineStr">
@@ -71303,19 +71303,19 @@
     </row>
     <row r="1597">
       <c r="A1597" s="2" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Aluguel de terno para Nicholas (2 / 2)</t>
+          <t>Sacos para os alimentos dos necessitados (2 / 2)</t>
         </is>
       </c>
       <c r="C1597" s="3" t="n">
-        <v>-175</v>
+        <v>-72</v>
       </c>
       <c r="D1597" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1597" t="inlineStr">
@@ -71330,12 +71330,12 @@
       </c>
       <c r="G1597" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1597" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1597" t="inlineStr">
@@ -71346,24 +71346,24 @@
     </row>
     <row r="1598">
       <c r="A1598" s="2" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (02)</t>
+          <t>Materiais de limpeza (2 / 2)</t>
         </is>
       </c>
       <c r="C1598" s="3" t="n">
-        <v>-1063.47</v>
+        <v>-110.2</v>
       </c>
       <c r="D1598" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1598" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1598" t="inlineStr">
@@ -71373,17 +71373,12 @@
       </c>
       <c r="G1598" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1598" t="inlineStr">
-        <is>
-          <t>Contas da casa</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1598" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1598" t="inlineStr">
@@ -71394,24 +71389,24 @@
     </row>
     <row r="1599">
       <c r="A1599" s="2" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Apt. SP. - Condomínio (02)</t>
         </is>
       </c>
       <c r="C1599" s="3" t="n">
-        <v>-53.66</v>
+        <v>-1063.47</v>
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1599" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1599" t="inlineStr">
@@ -71426,7 +71421,7 @@
       </c>
       <c r="H1599" t="inlineStr">
         <is>
-          <t>Manutenção e encargos</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1599" t="inlineStr">
@@ -71442,19 +71437,19 @@
     </row>
     <row r="1600">
       <c r="A1600" s="2" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Aluguel de terno para Nicholas (2 / 2)</t>
         </is>
       </c>
       <c r="C1600" s="3" t="n">
-        <v>-112.07</v>
+        <v>-175</v>
       </c>
       <c r="D1600" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1600" t="inlineStr">
@@ -71469,17 +71464,12 @@
       </c>
       <c r="G1600" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1600" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1600" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1600" t="inlineStr">
@@ -71490,19 +71480,19 @@
     </row>
     <row r="1601">
       <c r="A1601" s="2" t="n">
-        <v>46350</v>
+        <v>46348</v>
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Lata de lixo e outros utensílios domésticos</t>
         </is>
       </c>
       <c r="C1601" s="3" t="n">
-        <v>-500</v>
+        <v>-53.66</v>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1601" t="inlineStr">
@@ -71517,17 +71507,17 @@
       </c>
       <c r="G1601" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1601" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1601" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1601" t="inlineStr">
@@ -71538,24 +71528,24 @@
     </row>
     <row r="1602">
       <c r="A1602" s="2" t="n">
-        <v>46351</v>
+        <v>46348</v>
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>Pagamento "DUO GOURMET"</t>
+          <t>Casa Aracaju - Materiais para o jardim</t>
         </is>
       </c>
       <c r="C1602" s="3" t="n">
-        <v>-45</v>
+        <v>-112.07</v>
       </c>
       <c r="D1602" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1602" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1602" t="inlineStr">
@@ -71565,12 +71555,17 @@
       </c>
       <c r="G1602" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1602" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1602" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1602" t="inlineStr">
@@ -71581,19 +71576,19 @@
     </row>
     <row r="1603">
       <c r="A1603" s="2" t="n">
-        <v>46353</v>
+        <v>46350</v>
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
         </is>
       </c>
       <c r="C1603" s="3" t="n">
-        <v>-102.5</v>
+        <v>-500</v>
       </c>
       <c r="D1603" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1603" t="inlineStr">
@@ -71608,12 +71603,17 @@
       </c>
       <c r="G1603" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1603" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1603" t="inlineStr">
@@ -71624,24 +71624,24 @@
     </row>
     <row r="1604">
       <c r="A1604" s="2" t="n">
-        <v>46353</v>
+        <v>46351</v>
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Pagamento "DUO GOURMET"</t>
         </is>
       </c>
       <c r="C1604" s="3" t="n">
-        <v>-139</v>
+        <v>-45</v>
       </c>
       <c r="D1604" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1604" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1604" t="inlineStr">
@@ -71651,35 +71651,35 @@
       </c>
       <c r="G1604" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1604" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1604" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" s="2" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B1605" t="inlineStr">
         <is>
-          <t>TV SAMSUNG quarto do casal (7 / 8)</t>
+          <t>Aquisição do celular MOTOROLA G86</t>
         </is>
       </c>
       <c r="C1605" s="3" t="n">
-        <v>-337.49</v>
+        <v>-139</v>
       </c>
       <c r="D1605" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1605" t="inlineStr">
@@ -71694,40 +71694,40 @@
       </c>
       <c r="G1605" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1605" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1605" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" s="2" t="n">
-        <v>46357</v>
+        <v>46353</v>
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>Seguro Apt Aracaju - Parcelas 4</t>
+          <t>Troca da bateria do MACBOOK PRO</t>
         </is>
       </c>
       <c r="C1606" s="3" t="n">
-        <v>-52.85</v>
+        <v>-102.5</v>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E1606" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1606" t="inlineStr">
@@ -71737,12 +71737,12 @@
       </c>
       <c r="G1606" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I1606" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J1606" t="inlineStr">
@@ -71753,24 +71753,24 @@
     </row>
     <row r="1607">
       <c r="A1607" s="2" t="n">
-        <v>46358</v>
+        <v>46354</v>
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Seguro de Itens Pessoais</t>
+          <t>TV SAMSUNG quarto do casal (7 / 8)</t>
         </is>
       </c>
       <c r="C1607" s="3" t="n">
-        <v>-9.9</v>
+        <v>-337.49</v>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1607" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1607" t="inlineStr">
@@ -71780,12 +71780,12 @@
       </c>
       <c r="G1607" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1607" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1607" t="inlineStr">
@@ -71796,19 +71796,19 @@
     </row>
     <row r="1608">
       <c r="A1608" s="2" t="n">
-        <v>46362</v>
+        <v>46357</v>
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
+          <t>Seguro Apt Aracaju - Parcelas 4</t>
         </is>
       </c>
       <c r="C1608" s="3" t="n">
-        <v>-17600</v>
+        <v>-52.85</v>
       </c>
       <c r="D1608" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="E1608" t="inlineStr">
@@ -71823,40 +71823,40 @@
       </c>
       <c r="G1608" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1608" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1608" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" s="2" t="n">
-        <v>46362</v>
+        <v>46358</v>
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Película para RANGER XLT</t>
+          <t>Seguro de Itens Pessoais</t>
         </is>
       </c>
       <c r="C1609" s="3" t="n">
-        <v>-100</v>
+        <v>-9.9</v>
       </c>
       <c r="D1609" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Equipamentos Eletrônicos</t>
         </is>
       </c>
       <c r="E1609" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1609" t="inlineStr">
@@ -71866,17 +71866,12 @@
       </c>
       <c r="G1609" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1609" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1609" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1609" t="inlineStr">
@@ -71887,24 +71882,24 @@
     </row>
     <row r="1610">
       <c r="A1610" s="2" t="n">
-        <v>46364</v>
+        <v>46362</v>
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
+          <t>Casa Aracaju - Aquisição e instalação da piscina</t>
         </is>
       </c>
       <c r="C1610" s="3" t="n">
-        <v>-124.64</v>
+        <v>-17600</v>
       </c>
       <c r="D1610" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1610" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1610" t="inlineStr">
@@ -71914,40 +71909,35 @@
       </c>
       <c r="G1610" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1610" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1610" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1610" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" s="2" t="n">
-        <v>46364</v>
+        <v>46362</v>
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
+          <t>Película para RANGER XLT</t>
         </is>
       </c>
       <c r="C1611" s="3" t="n">
-        <v>-540.29</v>
+        <v>-100</v>
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1611" t="inlineStr">
@@ -71962,17 +71952,17 @@
       </c>
       <c r="G1611" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="H1611" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1611" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1611" t="inlineStr">
@@ -71983,24 +71973,24 @@
     </row>
     <row r="1612">
       <c r="A1612" s="2" t="n">
-        <v>46366</v>
+        <v>46364</v>
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Mensalidade da hidroginástica (11 / 11)</t>
+          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
         </is>
       </c>
       <c r="C1612" s="3" t="n">
-        <v>-23.46</v>
+        <v>-124.64</v>
       </c>
       <c r="D1612" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1612" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1612" t="inlineStr">
@@ -72010,12 +72000,17 @@
       </c>
       <c r="G1612" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1612" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1612" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1612" t="inlineStr">
@@ -72026,24 +72021,24 @@
     </row>
     <row r="1613">
       <c r="A1613" s="2" t="n">
-        <v>46366</v>
+        <v>46364</v>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>Plano OSAF - Serviços Funerários</t>
+          <t>Pagamento do estorno da AIR CANADA (1 e 2) em 02.03.2026</t>
         </is>
       </c>
       <c r="C1613" s="3" t="n">
-        <v>-82.64</v>
+        <v>-540.29</v>
       </c>
       <c r="D1613" t="inlineStr">
         <is>
-          <t>Serviços Funerários</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1613" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1613" t="inlineStr">
@@ -72053,12 +72048,17 @@
       </c>
       <c r="G1613" t="inlineStr">
         <is>
-          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1613" t="inlineStr">
         <is>
-          <t>Despesas com Seguros</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1613" t="inlineStr">
@@ -72073,15 +72073,15 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>Presentes comprados por Gracinha (2026.10.14)</t>
+          <t>Hotel Stela Maris - Salvador</t>
         </is>
       </c>
       <c r="C1614" s="3" t="n">
-        <v>-134.38</v>
+        <v>-69.37</v>
       </c>
       <c r="D1614" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1614" t="inlineStr">
@@ -72096,12 +72096,17 @@
       </c>
       <c r="G1614" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1614" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1614" t="inlineStr">
@@ -72116,15 +72121,15 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>Aplicação PGBL BRASILPREV - ACMD</t>
+          <t>Mensalidade da hidroginástica (11 / 11)</t>
         </is>
       </c>
       <c r="C1615" s="3" t="n">
-        <v>-209.34</v>
+        <v>-23.46</v>
       </c>
       <c r="D1615" t="inlineStr">
         <is>
-          <t>BRASILPREV</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="E1615" t="inlineStr">
@@ -72139,17 +72144,17 @@
       </c>
       <c r="G1615" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1615" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1615" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -72159,15 +72164,15 @@
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>Hotel Stela Maris - Salvador</t>
+          <t>Aplicação PGBL BRASILPREV - ACMD</t>
         </is>
       </c>
       <c r="C1616" s="3" t="n">
-        <v>-69.37</v>
+        <v>-209.34</v>
       </c>
       <c r="D1616" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>BRASILPREV</t>
         </is>
       </c>
       <c r="E1616" t="inlineStr">
@@ -72182,45 +72187,40 @@
       </c>
       <c r="G1616" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1616" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1616" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1616" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" s="2" t="n">
-        <v>46367</v>
+        <v>46366</v>
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
+          <t>Presentes comprados por Gracinha (2026.10.14)</t>
         </is>
       </c>
       <c r="C1617" s="3" t="n">
-        <v>-1818.04</v>
+        <v>-134.38</v>
       </c>
       <c r="D1617" t="inlineStr">
         <is>
-          <t>Ampliação-Melhorias Imóveis</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1617" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1617" t="inlineStr">
@@ -72230,40 +72230,40 @@
       </c>
       <c r="G1617" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1617" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1617" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" s="2" t="n">
-        <v>46369</v>
+        <v>46366</v>
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
+          <t>Plano OSAF - Serviços Funerários</t>
         </is>
       </c>
       <c r="C1618" s="3" t="n">
-        <v>-93.89</v>
+        <v>-82.64</v>
       </c>
       <c r="D1618" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>Serviços Funerários</t>
         </is>
       </c>
       <c r="E1618" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1618" t="inlineStr">
@@ -72273,17 +72273,12 @@
       </c>
       <c r="G1618" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1618" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>SEGUROS E SERVIÇOS FUNERÁRIOS</t>
         </is>
       </c>
       <c r="I1618" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Despesas com Seguros</t>
         </is>
       </c>
       <c r="J1618" t="inlineStr">
@@ -72294,19 +72289,19 @@
     </row>
     <row r="1619">
       <c r="A1619" s="2" t="n">
-        <v>46369</v>
+        <v>46367</v>
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>Seguro da Hilux SW4</t>
+          <t>Casa Aracaju - Toldo de proteção para a garagem</t>
         </is>
       </c>
       <c r="C1619" s="3" t="n">
-        <v>-233.11</v>
+        <v>-1818.04</v>
       </c>
       <c r="D1619" t="inlineStr">
         <is>
-          <t>Automóvel/Seguro</t>
+          <t>Ampliação-Melhorias Imóveis</t>
         </is>
       </c>
       <c r="E1619" t="inlineStr">
@@ -72321,22 +72316,17 @@
       </c>
       <c r="G1619" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
-        </is>
-      </c>
-      <c r="H1619" t="inlineStr">
-        <is>
-          <t>Automóvel</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1619" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Seguros)</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1619" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
@@ -72346,15 +72336,15 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
+          <t>Ajuste Seguro HILUX SW4 para a RANGER XLT</t>
         </is>
       </c>
       <c r="C1620" s="3" t="n">
-        <v>-58.07</v>
+        <v>-93.89</v>
       </c>
       <c r="D1620" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1620" t="inlineStr">
@@ -72369,35 +72359,40 @@
       </c>
       <c r="G1620" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1620" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1620" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" s="2" t="n">
-        <v>46371</v>
+        <v>46369</v>
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>Pagamento Clube SMILES</t>
+          <t>Seguro da Hilux SW4</t>
         </is>
       </c>
       <c r="C1621" s="3" t="n">
-        <v>-46</v>
+        <v>-233.11</v>
       </c>
       <c r="D1621" t="inlineStr">
         <is>
-          <t>VIAGENS/Passagens</t>
+          <t>Automóvel/Seguro</t>
         </is>
       </c>
       <c r="E1621" t="inlineStr">
@@ -72412,17 +72407,17 @@
       </c>
       <c r="G1621" t="inlineStr">
         <is>
-          <t>LAZER</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="H1621" t="inlineStr">
         <is>
-          <t>VIAGENS</t>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1621" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Automóvel (Seguros)</t>
         </is>
       </c>
       <c r="J1621" t="inlineStr">
@@ -72433,19 +72428,19 @@
     </row>
     <row r="1622">
       <c r="A1622" s="2" t="n">
-        <v>46371</v>
+        <v>46369</v>
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Casa Aracaju - Cabo PP para interligar o carregador de Bateria do BYD</t>
         </is>
       </c>
       <c r="C1622" s="3" t="n">
-        <v>-52.83</v>
+        <v>-58.07</v>
       </c>
       <c r="D1622" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Eletrônicos</t>
         </is>
       </c>
       <c r="E1622" t="inlineStr">
@@ -72460,35 +72455,35 @@
       </c>
       <c r="G1622" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1622" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Investimentos Bens</t>
         </is>
       </c>
       <c r="J1622" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" s="2" t="n">
-        <v>46372</v>
+        <v>46371</v>
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>Transporte Terrestre, Hoteis e Excursão</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1623" s="3" t="n">
-        <v>-1824.26</v>
+        <v>-52.83</v>
       </c>
       <c r="D1623" t="inlineStr">
         <is>
-          <t>VIAGENS/Passeios</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1623" t="inlineStr">
@@ -72503,17 +72498,12 @@
       </c>
       <c r="G1623" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1623" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1623" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1623" t="inlineStr">
@@ -72524,19 +72514,19 @@
     </row>
     <row r="1624">
       <c r="A1624" s="2" t="n">
-        <v>46375</v>
+        <v>46371</v>
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Pagamento Clube SMILES</t>
         </is>
       </c>
       <c r="C1624" s="3" t="n">
-        <v>-8.99</v>
+        <v>-46</v>
       </c>
       <c r="D1624" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>VIAGENS/Passagens</t>
         </is>
       </c>
       <c r="E1624" t="inlineStr">
@@ -72551,12 +72541,17 @@
       </c>
       <c r="G1624" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1624" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1624" t="inlineStr">
@@ -72567,19 +72562,19 @@
     </row>
     <row r="1625">
       <c r="A1625" s="2" t="n">
-        <v>46378</v>
+        <v>46372</v>
       </c>
       <c r="B1625" t="inlineStr">
         <is>
-          <t>Lata de lixo e outros utensílios domésticos</t>
+          <t>Transporte Terrestre, Hoteis e Excursão</t>
         </is>
       </c>
       <c r="C1625" s="3" t="n">
-        <v>-53.66</v>
+        <v>-1824.26</v>
       </c>
       <c r="D1625" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>VIAGENS/Passeios</t>
         </is>
       </c>
       <c r="E1625" t="inlineStr">
@@ -72594,17 +72589,17 @@
       </c>
       <c r="G1625" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1625" t="inlineStr">
         <is>
-          <t>Manutenção e encargos</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1625" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1625" t="inlineStr">
@@ -72615,19 +72610,19 @@
     </row>
     <row r="1626">
       <c r="A1626" s="2" t="n">
-        <v>46378</v>
+        <v>46375</v>
       </c>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>Casa Aracaju - Materiais para o jardim</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1626" s="3" t="n">
-        <v>-112.07</v>
+        <v>-8.99</v>
       </c>
       <c r="D1626" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1626" t="inlineStr">
@@ -72642,17 +72637,12 @@
       </c>
       <c r="G1626" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1626" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1626" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1626" t="inlineStr">
@@ -72663,19 +72653,19 @@
     </row>
     <row r="1627">
       <c r="A1627" s="2" t="n">
-        <v>46380</v>
+        <v>46378</v>
       </c>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
+          <t>Lata de lixo e outros utensílios domésticos</t>
         </is>
       </c>
       <c r="C1627" s="3" t="n">
-        <v>-500</v>
+        <v>-53.66</v>
       </c>
       <c r="D1627" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1627" t="inlineStr">
@@ -72690,17 +72680,17 @@
       </c>
       <c r="G1627" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1627" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1627" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1627" t="inlineStr">
@@ -72711,19 +72701,19 @@
     </row>
     <row r="1628">
       <c r="A1628" s="2" t="n">
-        <v>46383</v>
+        <v>46378</v>
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>Troca da bateria do MACBOOK PRO</t>
+          <t>Casa Aracaju - Materiais para o jardim</t>
         </is>
       </c>
       <c r="C1628" s="3" t="n">
-        <v>-102.5</v>
+        <v>-112.07</v>
       </c>
       <c r="D1628" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1628" t="inlineStr">
@@ -72738,12 +72728,17 @@
       </c>
       <c r="G1628" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>IMÓVEIS</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr">
+        <is>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1628" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1628" t="inlineStr">
@@ -72754,19 +72749,19 @@
     </row>
     <row r="1629">
       <c r="A1629" s="2" t="n">
-        <v>46383</v>
+        <v>46380</v>
       </c>
       <c r="B1629" t="inlineStr">
         <is>
-          <t>Aquisição do celular MOTOROLA G86</t>
+          <t>Instalação das câmeras lateral e frontal na RANGER xLT</t>
         </is>
       </c>
       <c r="C1629" s="3" t="n">
-        <v>-139</v>
+        <v>-500</v>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
-          <t>Eletrônicos</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1629" t="inlineStr">
@@ -72781,65 +72776,156 @@
       </c>
       <c r="G1629" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1629" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1629" t="inlineStr">
         <is>
-          <t>Investimentos Bens</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1629" t="inlineStr">
         <is>
-          <t>Investimentos</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" s="2" t="n">
+        <v>46383</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Troca da bateria do MACBOOK PRO</t>
+        </is>
+      </c>
+      <c r="C1630" s="3" t="n">
+        <v>-102.5</v>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>OUTRAS DESPESAS</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>OUTRAS DESPESAS</t>
+        </is>
+      </c>
+      <c r="I1630" t="inlineStr">
+        <is>
+          <t>Outras Despesas</t>
+        </is>
+      </c>
+      <c r="J1630" t="inlineStr">
+        <is>
+          <t>Despesas e Custos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="2" t="n">
+        <v>46383</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Aquisição do celular MOTOROLA G86</t>
+        </is>
+      </c>
+      <c r="C1631" s="3" t="n">
+        <v>-139</v>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>Eletrônicos</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>BENS DURÁVEIS</t>
+        </is>
+      </c>
+      <c r="I1631" t="inlineStr">
+        <is>
+          <t>Investimentos Bens</t>
+        </is>
+      </c>
+      <c r="J1631" t="inlineStr">
+        <is>
+          <t>Investimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="2" t="n">
         <v>46384</v>
       </c>
-      <c r="B1630" t="inlineStr">
+      <c r="B1632" t="inlineStr">
         <is>
           <t>TV SAMSUNG quarto do casal (8 / 8)</t>
         </is>
       </c>
-      <c r="C1630" s="3" t="n">
+      <c r="C1632" s="3" t="n">
         <v>-337.48</v>
       </c>
-      <c r="D1630" t="inlineStr">
+      <c r="D1632" t="inlineStr">
         <is>
           <t>Acessórios</t>
         </is>
       </c>
-      <c r="E1630" t="inlineStr">
-        <is>
-          <t>Cartão BB VISA</t>
-        </is>
-      </c>
-      <c r="F1630" t="inlineStr">
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>Cartão BB VISA</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="G1630" t="inlineStr">
+      <c r="G1632" t="inlineStr">
         <is>
           <t>FAMÍLIA</t>
         </is>
       </c>
-      <c r="I1630" t="inlineStr">
+      <c r="I1632" t="inlineStr">
         <is>
           <t>Despesas com família</t>
         </is>
       </c>
-      <c r="J1630" t="inlineStr">
+      <c r="J1632" t="inlineStr">
         <is>
           <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1630"/>
+  <autoFilter ref="A1:J1632"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Arquivos_Origem/Registros_2026.xlsx
+++ b/Arquivos_Origem/Registros_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transações" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transações" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transações'!$A$1:$J$1632</definedName>
@@ -64824,15 +64824,15 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Sapato para ACMD</t>
+          <t>Assinatura anual YouTube Premium</t>
         </is>
       </c>
       <c r="C1451" s="3" t="n">
-        <v>-121.6</v>
+        <v>-269</v>
       </c>
       <c r="D1451" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Assinaturas e Software</t>
         </is>
       </c>
       <c r="E1451" t="inlineStr">
@@ -64847,12 +64847,12 @@
       </c>
       <c r="G1451" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1451" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1451" t="inlineStr">
@@ -64867,35 +64867,35 @@
       </c>
       <c r="B1452" t="inlineStr">
         <is>
-          <t>Assinatura anual YouTube Premium</t>
+          <t>Adaptador Douglas de Tela sem fio 4k WiFi Hdmi</t>
         </is>
       </c>
       <c r="C1452" s="3" t="n">
-        <v>-269</v>
+        <v>-228.92</v>
       </c>
       <c r="D1452" t="inlineStr">
         <is>
-          <t>Assinaturas e Software</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1452" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1452" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1452" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1452" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1452" t="inlineStr">
@@ -64910,35 +64910,40 @@
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Adaptador Douglas de Tela sem fio 4k WiFi Hdmi</t>
+          <t>Película para RANGER XLT (Parabrisa) (7 / 7)</t>
         </is>
       </c>
       <c r="C1453" s="3" t="n">
-        <v>-228.92</v>
+        <v>-107.14</v>
       </c>
       <c r="D1453" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Automóvel/Manutenção</t>
         </is>
       </c>
       <c r="E1453" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1453" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1453" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>Automóvel</t>
         </is>
       </c>
       <c r="I1453" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com Automóvel (Manutenção)</t>
         </is>
       </c>
       <c r="J1453" t="inlineStr">
@@ -64953,15 +64958,15 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Película para RANGER XLT (Parabrisa) (7 / 7)</t>
+          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
         </is>
       </c>
       <c r="C1454" s="3" t="n">
-        <v>-107.14</v>
+        <v>-124.64</v>
       </c>
       <c r="D1454" t="inlineStr">
         <is>
-          <t>Automóvel/Manutenção</t>
+          <t>VIAGENS/Estadia</t>
         </is>
       </c>
       <c r="E1454" t="inlineStr">
@@ -64976,17 +64981,17 @@
       </c>
       <c r="G1454" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>LAZER</t>
         </is>
       </c>
       <c r="H1454" t="inlineStr">
         <is>
-          <t>Automóvel</t>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1454" t="inlineStr">
         <is>
-          <t>Despesas com Automóvel (Manutenção)</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1454" t="inlineStr">
@@ -65001,15 +65006,15 @@
       </c>
       <c r="B1455" t="inlineStr">
         <is>
-          <t>Pousada Aldeola em Baixio / Bahia (estadia)</t>
+          <t>Sapato para ACMD</t>
         </is>
       </c>
       <c r="C1455" s="3" t="n">
-        <v>-124.64</v>
+        <v>-121.6</v>
       </c>
       <c r="D1455" t="inlineStr">
         <is>
-          <t>VIAGENS/Estadia</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1455" t="inlineStr">
@@ -65024,17 +65029,12 @@
       </c>
       <c r="G1455" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1455" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1455" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1455" t="inlineStr">
@@ -65092,40 +65092,45 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Almoço com Gracinha</t>
+          <t>Adiantamento  PETROS</t>
         </is>
       </c>
       <c r="C1457" s="3" t="n">
-        <v>-165.27</v>
+        <v>6212.99</v>
       </c>
       <c r="D1457" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Benefícios Aposentadoria</t>
         </is>
       </c>
       <c r="E1457" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1457" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1457" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>Trabalho e Benefícios</t>
         </is>
       </c>
       <c r="I1457" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1457" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
@@ -65135,15 +65140,15 @@
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Silicone vedante para o Banheiro</t>
+          <t>Almoço com Gracinha</t>
         </is>
       </c>
       <c r="C1458" s="3" t="n">
-        <v>-18.9</v>
+        <v>-165.27</v>
       </c>
       <c r="D1458" t="inlineStr">
         <is>
-          <t>Restauração e Manutenção</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1458" t="inlineStr">
@@ -65158,17 +65163,12 @@
       </c>
       <c r="G1458" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
-        </is>
-      </c>
-      <c r="H1458" t="inlineStr">
-        <is>
-          <t>Manutenção e encargos</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1458" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1458" t="inlineStr">
@@ -65183,45 +65183,45 @@
       </c>
       <c r="B1459" t="inlineStr">
         <is>
-          <t>Adiantamento  PETROS</t>
+          <t>Silicone vedante para o Banheiro</t>
         </is>
       </c>
       <c r="C1459" s="3" t="n">
-        <v>6212.99</v>
+        <v>-18.9</v>
       </c>
       <c r="D1459" t="inlineStr">
         <is>
-          <t>Benefícios Aposentadoria</t>
+          <t>Restauração e Manutenção</t>
         </is>
       </c>
       <c r="E1459" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1459" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1459" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1459" t="inlineStr">
         <is>
-          <t>Trabalho e Benefícios</t>
+          <t>Manutenção e encargos</t>
         </is>
       </c>
       <c r="I1459" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1459" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -66589,15 +66589,15 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Amortização de Investimento - CRI TENDA ATA</t>
+          <t>Juros de Investimentos - DEB CPFL 1</t>
         </is>
       </c>
       <c r="C1491" s="3" t="n">
-        <v>35974.88</v>
+        <v>9970.889999999999</v>
       </c>
       <c r="D1491" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Juros de Investimento</t>
         </is>
       </c>
       <c r="E1491" t="inlineStr">
@@ -66612,7 +66612,12 @@
       </c>
       <c r="G1491" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>Financeiras</t>
         </is>
       </c>
       <c r="I1491" t="inlineStr">
@@ -66857,15 +66862,15 @@
       </c>
       <c r="B1497" t="inlineStr">
         <is>
-          <t>Conserto da mala</t>
+          <t>Utilização por um mes da IA CLAUDE 1</t>
         </is>
       </c>
       <c r="C1497" s="3" t="n">
-        <v>-50</v>
+        <v>-110</v>
       </c>
       <c r="D1497" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>Assinaturas e Software</t>
         </is>
       </c>
       <c r="E1497" t="inlineStr">
@@ -66880,12 +66885,12 @@
       </c>
       <c r="G1497" t="inlineStr">
         <is>
-          <t>OUTRAS DESPESAS</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1497" t="inlineStr">
         <is>
-          <t>Outras Despesas</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1497" t="inlineStr">
@@ -66900,7 +66905,7 @@
       </c>
       <c r="B1498" t="inlineStr">
         <is>
-          <t>Utilização por um mes da IA CLAUDE 1</t>
+          <t>Utilização por um mes da IA CLAUDE 2</t>
         </is>
       </c>
       <c r="C1498" s="3" t="n">
@@ -66943,15 +66948,15 @@
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Utilização por um mes da IA CLAUDE 2</t>
+          <t>IOF do pagamento da IA CLAUDE</t>
         </is>
       </c>
       <c r="C1499" s="3" t="n">
-        <v>-110</v>
+        <v>-3.85</v>
       </c>
       <c r="D1499" t="inlineStr">
         <is>
-          <t>Assinaturas e Software</t>
+          <t>Tarifas Bancárias</t>
         </is>
       </c>
       <c r="E1499" t="inlineStr">
@@ -66966,12 +66971,12 @@
       </c>
       <c r="G1499" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>SERVIÇOS FINANCEIROS</t>
         </is>
       </c>
       <c r="I1499" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas Bancárias</t>
         </is>
       </c>
       <c r="J1499" t="inlineStr">
@@ -66986,40 +66991,40 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>IOF do pagamento da IA CLAUDE</t>
+          <t>Residencial San Juan - Lote 81 - Parcela 22</t>
         </is>
       </c>
       <c r="C1500" s="3" t="n">
-        <v>-3.85</v>
+        <v>-12224.85</v>
       </c>
       <c r="D1500" t="inlineStr">
         <is>
-          <t>Tarifas Bancárias</t>
+          <t>Aquisição Imóveis</t>
         </is>
       </c>
       <c r="E1500" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1500" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1500" t="inlineStr">
         <is>
-          <t>SERVIÇOS FINANCEIROS</t>
+          <t>BENS DURÁVEIS</t>
         </is>
       </c>
       <c r="I1500" t="inlineStr">
         <is>
-          <t>Despesas Bancárias</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
       <c r="J1500" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Bens Imóveis</t>
         </is>
       </c>
     </row>
@@ -67029,15 +67034,15 @@
       </c>
       <c r="B1501" t="inlineStr">
         <is>
-          <t>Residencial San Juan - Lote 81 - Parcela 22</t>
+          <t>Água de côco e suco de laranja</t>
         </is>
       </c>
       <c r="C1501" s="3" t="n">
-        <v>-12224.85</v>
+        <v>-20</v>
       </c>
       <c r="D1501" t="inlineStr">
         <is>
-          <t>Aquisição Imóveis</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1501" t="inlineStr">
@@ -67052,17 +67057,17 @@
       </c>
       <c r="G1501" t="inlineStr">
         <is>
-          <t>BENS DURÁVEIS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1501" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1501" t="inlineStr">
         <is>
-          <t>Investimentos Bens Imóveis</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -67072,15 +67077,15 @@
       </c>
       <c r="B1502" t="inlineStr">
         <is>
-          <t>Água de côco e suco de laranja</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1502" s="3" t="n">
-        <v>-20</v>
+        <v>-38000</v>
       </c>
       <c r="D1502" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1502" t="inlineStr">
@@ -67095,17 +67100,17 @@
       </c>
       <c r="G1502" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1502" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1502" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -67115,15 +67120,15 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Juros de Investimentos - CRI TENDA ATA</t>
         </is>
       </c>
       <c r="C1503" s="3" t="n">
-        <v>-38000</v>
+        <v>3703.51</v>
       </c>
       <c r="D1503" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>Juros de Investimento</t>
         </is>
       </c>
       <c r="E1503" t="inlineStr">
@@ -67138,17 +67143,22 @@
       </c>
       <c r="G1503" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>Financeiras</t>
         </is>
       </c>
       <c r="I1503" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1503" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -67158,15 +67168,15 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Juros de Investimentos - CRI TENDA ATA</t>
+          <t>Amortização de Investimento - CRI TENDA ATA</t>
         </is>
       </c>
       <c r="C1504" s="3" t="n">
-        <v>3703.51</v>
+        <v>35974.88</v>
       </c>
       <c r="D1504" t="inlineStr">
         <is>
-          <t>Juros de Investimento</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1504" t="inlineStr">
@@ -67181,12 +67191,7 @@
       </c>
       <c r="G1504" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H1504" t="inlineStr">
-        <is>
-          <t>Financeiras</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1504" t="inlineStr">
@@ -67206,11 +67211,11 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Juros de Investimentos - DEB CPFL 1</t>
+          <t>Juros de Investimentos - DEB CPFL 2</t>
         </is>
       </c>
       <c r="C1505" s="3" t="n">
-        <v>9970.889999999999</v>
+        <v>9970.98</v>
       </c>
       <c r="D1505" t="inlineStr">
         <is>
@@ -67254,11 +67259,11 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>Juros de Investimentos - DEB CPFL 2</t>
+          <t>Juros de Investimentos - DEB CPFL</t>
         </is>
       </c>
       <c r="C1506" s="3" t="n">
-        <v>9970.98</v>
+        <v>10319.88</v>
       </c>
       <c r="D1506" t="inlineStr">
         <is>
@@ -67302,45 +67307,40 @@
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Juros de Investimentos - DEB CPFL</t>
+          <t>Conserto da mala, refazendo a costura.</t>
         </is>
       </c>
       <c r="C1507" s="3" t="n">
-        <v>10319.88</v>
+        <v>-50</v>
       </c>
       <c r="D1507" t="inlineStr">
         <is>
-          <t>Juros de Investimento</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="E1507" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1507" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1507" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="H1507" t="inlineStr">
-        <is>
-          <t>Financeiras</t>
+          <t>OUTRAS DESPESAS</t>
         </is>
       </c>
       <c r="I1507" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Outras Despesas</t>
         </is>
       </c>
       <c r="J1507" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -67350,45 +67350,40 @@
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>Transporte Terrestre, Hoteis e Excursão</t>
+          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
         </is>
       </c>
       <c r="C1508" s="3" t="n">
-        <v>-1824.26</v>
+        <v>-30000</v>
       </c>
       <c r="D1508" t="inlineStr">
         <is>
-          <t>VIAGENS/Passeios</t>
+          <t>Aplicação em Investimento</t>
         </is>
       </c>
       <c r="E1508" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1508" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1508" t="inlineStr">
         <is>
-          <t>LAZER</t>
-        </is>
-      </c>
-      <c r="H1508" t="inlineStr">
-        <is>
-          <t>VIAGENS</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1508" t="inlineStr">
         <is>
-          <t>Despesas com lazer</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
       <c r="J1508" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Investimentos Financeiros</t>
         </is>
       </c>
     </row>
@@ -67441,40 +67436,45 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Aplicação Investimento Financeiro - BB RF REF DI Pvt</t>
+          <t>Transporte Terrestre, Hoteis e Excursão</t>
         </is>
       </c>
       <c r="C1510" s="3" t="n">
-        <v>-30000</v>
+        <v>-1824.26</v>
       </c>
       <c r="D1510" t="inlineStr">
         <is>
-          <t>Aplicação em Investimento</t>
+          <t>VIAGENS/Passeios</t>
         </is>
       </c>
       <c r="E1510" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1510" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1510" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>LAZER</t>
+        </is>
+      </c>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>VIAGENS</t>
         </is>
       </c>
       <c r="I1510" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas com lazer</t>
         </is>
       </c>
       <c r="J1510" t="inlineStr">
         <is>
-          <t>Investimentos Financeiros</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -67484,15 +67484,15 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Alimentos</t>
         </is>
       </c>
       <c r="C1511" s="3" t="n">
-        <v>-55.81</v>
+        <v>-36.86</v>
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1511" t="inlineStr">
@@ -67507,12 +67507,12 @@
       </c>
       <c r="G1511" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1511" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1511" t="inlineStr">
@@ -67527,15 +67527,15 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>Papel para impressora</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1512" s="3" t="n">
-        <v>-7.7</v>
+        <v>-55.81</v>
       </c>
       <c r="D1512" t="inlineStr">
         <is>
-          <t>Material Escolar</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1512" t="inlineStr">
@@ -67550,12 +67550,12 @@
       </c>
       <c r="G1512" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1512" t="inlineStr">
         <is>
-          <t>Despesas com educação</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1512" t="inlineStr">
@@ -67570,15 +67570,15 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>Presentes ACMD e MGAP (6 / 6)</t>
+          <t>Papel para impressora</t>
         </is>
       </c>
       <c r="C1513" s="3" t="n">
-        <v>-106.8</v>
+        <v>-7.7</v>
       </c>
       <c r="D1513" t="inlineStr">
         <is>
-          <t>Presentes</t>
+          <t>Material Escolar</t>
         </is>
       </c>
       <c r="E1513" t="inlineStr">
@@ -67593,12 +67593,12 @@
       </c>
       <c r="G1513" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="I1513" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com educação</t>
         </is>
       </c>
       <c r="J1513" t="inlineStr">
@@ -67613,11 +67613,11 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Manteiga</t>
+          <t>Vassouras. e panos de chão</t>
         </is>
       </c>
       <c r="C1514" s="3" t="n">
-        <v>-22.36</v>
+        <v>-71.37</v>
       </c>
       <c r="D1514" t="inlineStr">
         <is>
@@ -67656,11 +67656,11 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Vassouras. e panos de chão</t>
+          <t>Manteiga</t>
         </is>
       </c>
       <c r="C1515" s="3" t="n">
-        <v>-71.37</v>
+        <v>-22.36</v>
       </c>
       <c r="D1515" t="inlineStr">
         <is>
@@ -67699,15 +67699,15 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Combustível para RANGER XLT</t>
+          <t>Presentes ACMD e MGAP (6 / 6)</t>
         </is>
       </c>
       <c r="C1516" s="3" t="n">
-        <v>-262.45</v>
+        <v>-106.8</v>
       </c>
       <c r="D1516" t="inlineStr">
         <is>
-          <t>Combustível</t>
+          <t>Presentes</t>
         </is>
       </c>
       <c r="E1516" t="inlineStr">
@@ -67722,12 +67722,12 @@
       </c>
       <c r="G1516" t="inlineStr">
         <is>
-          <t>TRANSPORTE</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1516" t="inlineStr">
         <is>
-          <t>Despesas com Combustível</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1516" t="inlineStr">
@@ -67742,15 +67742,15 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>Alimentos</t>
+          <t>Combustível para RANGER XLT</t>
         </is>
       </c>
       <c r="C1517" s="3" t="n">
-        <v>-36.86</v>
+        <v>-262.45</v>
       </c>
       <c r="D1517" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Combustível</t>
         </is>
       </c>
       <c r="E1517" t="inlineStr">
@@ -67765,12 +67765,12 @@
       </c>
       <c r="G1517" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>TRANSPORTE</t>
         </is>
       </c>
       <c r="I1517" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com Combustível</t>
         </is>
       </c>
       <c r="J1517" t="inlineStr">
@@ -67785,15 +67785,15 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Café da manhã com Gracinha</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1518" s="3" t="n">
-        <v>-65.67</v>
+        <v>-95.97</v>
       </c>
       <c r="D1518" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1518" t="inlineStr">
@@ -67808,12 +67808,12 @@
       </c>
       <c r="G1518" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1518" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1518" t="inlineStr">
@@ -67828,35 +67828,35 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Ajuda a Casa do Pobre</t>
         </is>
       </c>
       <c r="C1519" s="3" t="n">
-        <v>-95.97</v>
+        <v>-30</v>
       </c>
       <c r="D1519" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Doações e Ajudas</t>
         </is>
       </c>
       <c r="E1519" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1519" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1519" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>DOAÇÕES</t>
         </is>
       </c>
       <c r="I1519" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com doações</t>
         </is>
       </c>
       <c r="J1519" t="inlineStr">
@@ -67871,15 +67871,15 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>Ajuda a Casa do Pobre</t>
+          <t>Água de côco</t>
         </is>
       </c>
       <c r="C1520" s="3" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="D1520" t="inlineStr">
         <is>
-          <t>Doações e Ajudas</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1520" t="inlineStr">
@@ -67894,12 +67894,12 @@
       </c>
       <c r="G1520" t="inlineStr">
         <is>
-          <t>DOAÇÕES</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1520" t="inlineStr">
         <is>
-          <t>Despesas com doações</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1520" t="inlineStr">
@@ -67914,35 +67914,35 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>Água de côco</t>
+          <t>Utilização por um ano da IA CLAUDE</t>
         </is>
       </c>
       <c r="C1521" s="3" t="n">
-        <v>-10</v>
+        <v>-999.54</v>
       </c>
       <c r="D1521" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Assinaturas e Software</t>
         </is>
       </c>
       <c r="E1521" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1521" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1521" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1521" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1521" t="inlineStr">
@@ -67957,15 +67957,15 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Utilização por um ano da IA CLAUDE</t>
+          <t>Café da manhã com Gracinha</t>
         </is>
       </c>
       <c r="C1522" s="3" t="n">
-        <v>-999.54</v>
+        <v>-65.67</v>
       </c>
       <c r="D1522" t="inlineStr">
         <is>
-          <t>Assinaturas e Software</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="E1522" t="inlineStr">
@@ -67980,12 +67980,12 @@
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1522" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1522" t="inlineStr">
@@ -68000,35 +68000,35 @@
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Protetor Auricular (com abafador de ruído</t>
+          <t>Produtos Químicos para limpeza de piso externo</t>
         </is>
       </c>
       <c r="C1523" s="3" t="n">
-        <v>-51.99</v>
+        <v>-73.5</v>
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>Acessórios</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1523" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1523" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1523" t="inlineStr">
@@ -68043,35 +68043,35 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Perfume no Boticário</t>
+          <t>Celulares - VIVO</t>
         </is>
       </c>
       <c r="C1524" s="3" t="n">
-        <v>-8.99</v>
+        <v>-359.89</v>
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>Salão de Beleza e Cosméticos</t>
+          <t>Celular</t>
         </is>
       </c>
       <c r="E1524" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1524" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1524" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>TECNOLOGIA E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="I1524" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com TI</t>
         </is>
       </c>
       <c r="J1524" t="inlineStr">
@@ -68086,35 +68086,35 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Remédios para ACMD</t>
+          <t>Protetor Auricular (com abafador de ruído</t>
         </is>
       </c>
       <c r="C1525" s="3" t="n">
-        <v>-19.99</v>
+        <v>-51.99</v>
       </c>
       <c r="D1525" t="inlineStr">
         <is>
-          <t>Farmácia</t>
+          <t>Acessórios</t>
         </is>
       </c>
       <c r="E1525" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1525" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G1525" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1525" t="inlineStr">
         <is>
-          <t>Despesas com Saúde</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1525" t="inlineStr">
@@ -68129,15 +68129,15 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>Produtos Químicos para limpeza de piso externo</t>
+          <t>Perfume no Boticário</t>
         </is>
       </c>
       <c r="C1526" s="3" t="n">
-        <v>-73.5</v>
+        <v>-8.99</v>
       </c>
       <c r="D1526" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Salão de Beleza e Cosméticos</t>
         </is>
       </c>
       <c r="E1526" t="inlineStr">
@@ -68152,12 +68152,12 @@
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1526" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1526" t="inlineStr">
@@ -68172,35 +68172,35 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Celulares - VIVO</t>
+          <t>Remédios para ACMD</t>
         </is>
       </c>
       <c r="C1527" s="3" t="n">
-        <v>-359.89</v>
+        <v>-19.99</v>
       </c>
       <c r="D1527" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Farmácia</t>
         </is>
       </c>
       <c r="E1527" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1527" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G1527" t="inlineStr">
         <is>
-          <t>TECNOLOGIA E COMUNICAÇÃO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="I1527" t="inlineStr">
         <is>
-          <t>Despesas com TI</t>
+          <t>Despesas com Saúde</t>
         </is>
       </c>
       <c r="J1527" t="inlineStr">
@@ -68215,15 +68215,15 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Materiais de limpeza (1 / 2)</t>
+          <t>Frutas e verduras</t>
         </is>
       </c>
       <c r="C1528" s="3" t="n">
-        <v>-110.2</v>
+        <v>-238.59</v>
       </c>
       <c r="D1528" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Supermercado</t>
         </is>
       </c>
       <c r="E1528" t="inlineStr">
@@ -68258,20 +68258,20 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>Frutas e verduras</t>
+          <t>Resgate de Investimento - BB RF DEB INC PVT</t>
         </is>
       </c>
       <c r="C1529" s="3" t="n">
-        <v>-238.59</v>
+        <v>100000</v>
       </c>
       <c r="D1529" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Resgate de Investimento</t>
         </is>
       </c>
       <c r="E1529" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1529" t="inlineStr">
@@ -68281,17 +68281,17 @@
       </c>
       <c r="G1529" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>INVESTIMENTOS E PATRIMÔNIO</t>
         </is>
       </c>
       <c r="I1529" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
       <c r="J1529" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas Financeiras</t>
         </is>
       </c>
     </row>
@@ -68301,20 +68301,20 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>Sacos para os alimentos dos necessitados (1 / 2)</t>
+          <t>Pagamento DAE (09.2026) - Ivonilde</t>
         </is>
       </c>
       <c r="C1530" s="3" t="n">
-        <v>-72</v>
+        <v>-445.76</v>
       </c>
       <c r="D1530" t="inlineStr">
         <is>
-          <t>Feira e Mercearia</t>
+          <t>Encargos Empregados</t>
         </is>
       </c>
       <c r="E1530" t="inlineStr">
         <is>
-          <t>Cartão BB VISA</t>
+          <t>Conta BB</t>
         </is>
       </c>
       <c r="F1530" t="inlineStr">
@@ -68324,12 +68324,12 @@
       </c>
       <c r="G1530" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>EMPREGADOS</t>
         </is>
       </c>
       <c r="I1530" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com empregados</t>
         </is>
       </c>
       <c r="J1530" t="inlineStr">
@@ -68344,20 +68344,20 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Pagamento DAE (09.2026) - Ivonilde</t>
+          <t>Sacos para os alimentos dos necessitados (1 / 2)</t>
         </is>
       </c>
       <c r="C1531" s="3" t="n">
-        <v>-445.76</v>
+        <v>-72</v>
       </c>
       <c r="D1531" t="inlineStr">
         <is>
-          <t>Encargos Empregados</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1531" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1531" t="inlineStr">
@@ -68367,12 +68367,12 @@
       </c>
       <c r="G1531" t="inlineStr">
         <is>
-          <t>EMPREGADOS</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1531" t="inlineStr">
         <is>
-          <t>Despesas com empregados</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1531" t="inlineStr">
@@ -68387,20 +68387,20 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Resgate de Investimento - BB RF DEB INC PVT</t>
+          <t>Materiais de limpeza (1 / 2)</t>
         </is>
       </c>
       <c r="C1532" s="3" t="n">
-        <v>100000</v>
+        <v>-110.2</v>
       </c>
       <c r="D1532" t="inlineStr">
         <is>
-          <t>Resgate de Investimento</t>
+          <t>Feira e Mercearia</t>
         </is>
       </c>
       <c r="E1532" t="inlineStr">
         <is>
-          <t>Conta BB</t>
+          <t>Cartão BB VISA</t>
         </is>
       </c>
       <c r="F1532" t="inlineStr">
@@ -68410,17 +68410,17 @@
       </c>
       <c r="G1532" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS E PATRIMÔNIO</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1532" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1532" t="inlineStr">
         <is>
-          <t>Receitas Financeiras</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68430,15 +68430,15 @@
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Café da manhã com Gracinha</t>
+          <t>Aluguel de terno para Nicholas (1 / 2)</t>
         </is>
       </c>
       <c r="C1533" s="3" t="n">
-        <v>-39.75</v>
+        <v>-175</v>
       </c>
       <c r="D1533" t="inlineStr">
         <is>
-          <t>Padaria</t>
+          <t>Roupas e Calçados</t>
         </is>
       </c>
       <c r="E1533" t="inlineStr">
@@ -68453,12 +68453,12 @@
       </c>
       <c r="G1533" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO E LIMPEZA</t>
+          <t>FAMÍLIA</t>
         </is>
       </c>
       <c r="I1533" t="inlineStr">
         <is>
-          <t>Despesas com alimentação e limpeza</t>
+          <t>Despesas com família</t>
         </is>
       </c>
       <c r="J1533" t="inlineStr">
@@ -68516,15 +68516,15 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Devolução do valor da compra dia 08/10/2026</t>
+          <t>Apt. SP. - Condomínio (02)</t>
         </is>
       </c>
       <c r="C1535" s="3" t="n">
-        <v>228.92</v>
+        <v>-1063.47</v>
       </c>
       <c r="D1535" t="inlineStr">
         <is>
-          <t>Reembolso</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="E1535" t="inlineStr">
@@ -68539,22 +68539,22 @@
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>RECEITAS</t>
+          <t>IMÓVEIS</t>
         </is>
       </c>
       <c r="H1535" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Contas da casa</t>
         </is>
       </c>
       <c r="I1535" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas com imóveis</t>
         </is>
       </c>
       <c r="J1535" t="inlineStr">
         <is>
-          <t>Receitas e Benefícios</t>
+          <t>Despesas e Custos</t>
         </is>
       </c>
     </row>
@@ -68564,15 +68564,15 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Apt. SP. - Condomínio (02)</t>
+          <t>Devolução do valor da compra dia 08/10/2026</t>
         </is>
       </c>
       <c r="C1536" s="3" t="n">
-        <v>-1063.47</v>
+        <v>228.92</v>
       </c>
       <c r="D1536" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Reembolso</t>
         </is>
       </c>
       <c r="E1536" t="inlineStr">
@@ -68587,22 +68587,22 @@
       </c>
       <c r="G1536" t="inlineStr">
         <is>
-          <t>IMÓVEIS</t>
+          <t>RECEITAS</t>
         </is>
       </c>
       <c r="H1536" t="inlineStr">
         <is>
-          <t>Contas da casa</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="I1536" t="inlineStr">
         <is>
-          <t>Despesas com imóveis</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
       <c r="J1536" t="inlineStr">
         <is>
-          <t>Despesas e Custos</t>
+          <t>Receitas e Benefícios</t>
         </is>
       </c>
     </row>
@@ -68612,15 +68612,15 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Aluguel de terno para Nicholas (1 / 2)</t>
+          <t>Café da manhã com Gracinha</t>
         </is>
       </c>
       <c r="C1537" s="3" t="n">
-        <v>-175</v>
+        <v>-39.75</v>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
-          <t>Roupas e Calçados</t>
+          <t>Padaria</t>
         </is>
       </c>
       <c r="E1537" t="inlineStr">
@@ -68635,12 +68635,12 @@
       </c>
       <c r="G1537" t="inlineStr">
         <is>
-          <t>FAMÍLIA</t>
+          <t>ALIMENTAÇÃO E LIMPEZA</t>
         </is>
       </c>
       <c r="I1537" t="inlineStr">
         <is>
-          <t>Despesas com família</t>
+          <t>Despesas com alimentação e limpeza</t>
         </is>
       </c>
       <c r="J1537" t="inlineStr">

--- a/Arquivos_Origem/Registros_2026.xlsx
+++ b/Arquivos_Origem/Registros_2026.xlsx
@@ -69732,7 +69732,7 @@
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Alimentos</t>
+          <t>Alimentos e Materiais de Limpeza</t>
         </is>
       </c>
       <c r="C1562" s="3" t="n">
